--- a/hololive_cards.xlsx
+++ b/hololive_cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ff824d2898a640b1/デスクトップ/hololive_cards/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="11_AD4D066CA252ABDACC104873B990E4B073EEDF5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6908B69-C9E5-4A52-BD2F-0422D54C3759}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="11_AD4D066CA252ABDACC104873B990E4B073EEDF5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{213FBECD-F2EA-41EF-AA49-D23A7AF4AD78}"/>
   <bookViews>
-    <workbookView xWindow="10140" yWindow="1275" windowWidth="21375" windowHeight="8775" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12795" yWindow="195" windowWidth="15900" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="253">
   <si>
     <t>シリーズ名</t>
     <rPh sb="4" eb="5">
@@ -706,11 +706,108 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Vol1_01.jpg</t>
+    <t>ita-vol1_N-01.jpg</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Vol1_02.jpg</t>
+    <t>ita-vol1_N-02.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_N-03.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_N-04.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_N-05.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_N-06.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_N-07.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_N-08.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_N-09.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_N-10.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_N-11.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_N-12.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_N-13.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_N-14.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_N-15.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_N-16.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_N-17.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_P-01.jpg</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ita-vol1_P-02.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_P-03.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_P-04.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_P-05.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_P-06.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_P-07.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_P-08.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_P-09.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_P-10.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_P-11.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_P-12.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_P-13.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_P-14.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_P-15.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_P-16.jpg</t>
+  </si>
+  <si>
+    <t>ita-vol1_P-17.jpg</t>
   </si>
 </sst>
 </file>
@@ -1053,7 +1150,7 @@
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="3" width="20.625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.75" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1121,6 +1218,9 @@
       <c r="D4" s="2">
         <v>2</v>
       </c>
+      <c r="E4" s="1" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
@@ -1135,6 +1235,9 @@
       <c r="D5" s="2">
         <v>0</v>
       </c>
+      <c r="E5" s="1" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
@@ -1149,6 +1252,9 @@
       <c r="D6" s="2">
         <v>2</v>
       </c>
+      <c r="E6" s="1" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
@@ -1163,6 +1269,9 @@
       <c r="D7" s="2">
         <v>0</v>
       </c>
+      <c r="E7" s="1" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
@@ -1177,6 +1286,9 @@
       <c r="D8" s="2">
         <v>4</v>
       </c>
+      <c r="E8" s="1" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
@@ -1191,6 +1303,9 @@
       <c r="D9" s="2">
         <v>4</v>
       </c>
+      <c r="E9" s="1" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
@@ -1205,6 +1320,9 @@
       <c r="D10" s="2">
         <v>3</v>
       </c>
+      <c r="E10" s="1" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
@@ -1219,6 +1337,9 @@
       <c r="D11" s="2">
         <v>1</v>
       </c>
+      <c r="E11" s="1" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
@@ -1233,6 +1354,9 @@
       <c r="D12" s="2">
         <v>3</v>
       </c>
+      <c r="E12" s="1" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
@@ -1247,6 +1371,9 @@
       <c r="D13" s="2">
         <v>1</v>
       </c>
+      <c r="E13" s="1" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
@@ -1261,6 +1388,9 @@
       <c r="D14" s="2">
         <v>1</v>
       </c>
+      <c r="E14" s="1" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
@@ -1275,6 +1405,9 @@
       <c r="D15" s="2">
         <v>2</v>
       </c>
+      <c r="E15" s="1" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
@@ -1289,8 +1422,11 @@
       <c r="D16" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
@@ -1303,8 +1439,11 @@
       <c r="D17" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>4</v>
       </c>
@@ -1317,8 +1456,11 @@
       <c r="D18" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
         <v>4</v>
       </c>
@@ -1331,8 +1473,11 @@
       <c r="D19" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
         <v>4</v>
       </c>
@@ -1345,8 +1490,11 @@
       <c r="D20" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
         <v>4</v>
       </c>
@@ -1359,8 +1507,11 @@
       <c r="D21" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
         <v>4</v>
       </c>
@@ -1373,8 +1524,11 @@
       <c r="D22" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="E22" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
@@ -1387,8 +1541,11 @@
       <c r="D23" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="E23" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
@@ -1401,8 +1558,11 @@
       <c r="D24" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="E24" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
@@ -1415,8 +1575,11 @@
       <c r="D25" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="E25" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
@@ -1429,8 +1592,11 @@
       <c r="D26" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="E26" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
         <v>4</v>
       </c>
@@ -1443,8 +1609,11 @@
       <c r="D27" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="1:4">
+      <c r="E27" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
         <v>4</v>
       </c>
@@ -1457,8 +1626,11 @@
       <c r="D28" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="E28" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
         <v>4</v>
       </c>
@@ -1471,8 +1643,11 @@
       <c r="D29" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:4">
+      <c r="E29" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" s="1" t="s">
         <v>4</v>
       </c>
@@ -1485,8 +1660,11 @@
       <c r="D30" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="E30" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" s="1" t="s">
         <v>4</v>
       </c>
@@ -1499,8 +1677,11 @@
       <c r="D31" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:4">
+      <c r="E31" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
         <v>4</v>
       </c>
@@ -1513,8 +1694,11 @@
       <c r="D32" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="E32" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
         <v>4</v>
       </c>
@@ -1527,8 +1711,11 @@
       <c r="D33" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:4">
+      <c r="E33" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
         <v>4</v>
       </c>
@@ -1541,8 +1728,11 @@
       <c r="D34" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:4">
+      <c r="E34" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
@@ -1555,8 +1745,11 @@
       <c r="D35" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:4">
+      <c r="E35" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" s="1" t="s">
         <v>56</v>
       </c>
@@ -1570,7 +1763,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:5">
       <c r="A37" s="1" t="s">
         <v>56</v>
       </c>
@@ -1584,7 +1777,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:5">
       <c r="A38" s="1" t="s">
         <v>56</v>
       </c>
@@ -1598,7 +1791,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
         <v>56</v>
       </c>
@@ -1612,7 +1805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:5">
       <c r="A40" s="1" t="s">
         <v>56</v>
       </c>
@@ -1626,7 +1819,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:5">
       <c r="A41" s="1" t="s">
         <v>56</v>
       </c>
@@ -1640,7 +1833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:5">
       <c r="A42" s="1" t="s">
         <v>56</v>
       </c>
@@ -1654,7 +1847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:5">
       <c r="A43" s="1" t="s">
         <v>56</v>
       </c>
@@ -1668,7 +1861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:5">
       <c r="A44" s="1" t="s">
         <v>56</v>
       </c>
@@ -1682,7 +1875,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:5">
       <c r="A45" s="1" t="s">
         <v>56</v>
       </c>
@@ -1696,7 +1889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:5">
       <c r="A46" s="1" t="s">
         <v>56</v>
       </c>
@@ -1710,7 +1903,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:5">
       <c r="A47" s="1" t="s">
         <v>56</v>
       </c>
@@ -1724,7 +1917,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:5">
       <c r="A48" s="1" t="s">
         <v>56</v>
       </c>

--- a/hololive_cards.xlsx
+++ b/hololive_cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ff824d2898a640b1/デスクトップ/hololive_cards/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="11_AD4D066CA252ABDACC104873B990E4B073EEDF5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34AA2FEB-E084-4353-999E-833B0A423321}"/>
+  <xr:revisionPtr revIDLastSave="106" documentId="11_AD4D066CA252ABDACC104873B990E4B073EEDF5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63866911-93EB-4605-9166-56947E8045C4}"/>
   <bookViews>
-    <workbookView xWindow="12840" yWindow="195" windowWidth="15900" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3585" yWindow="480" windowWidth="12960" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1745,9 +1745,6 @@
     <t>waf-3_51.jpg</t>
   </si>
   <si>
-    <t>ホロライブ ウエハースVol.03</t>
-  </si>
-  <si>
     <t>ベスティア・ゼータ</t>
   </si>
   <si>
@@ -1905,9 +1902,6 @@
     <t>waf-vol3_49.jpg</t>
   </si>
   <si>
-    <t>ホロライブ ウエハースVol.04</t>
-  </si>
-  <si>
     <t>音乃瀬奏</t>
   </si>
   <si>
@@ -2014,9 +2008,6 @@
     <t>waf-vol4_31.jpg</t>
   </si>
   <si>
-    <t>ホロライブ ウエハースVol.05</t>
-  </si>
-  <si>
     <t>シオリ・ノヴェラ</t>
   </si>
   <si>
@@ -2159,12 +2150,6 @@
     <t>waf-vol5_33.jpg</t>
   </si>
   <si>
-    <t>ホロライブ ウエハースVol.06</t>
-  </si>
-  <si>
-    <t>ホロライブ ウエハースVol.07</t>
-  </si>
-  <si>
     <t>waf-vol6_01.jpg</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2353,9 +2338,6 @@
     <t>waf-vol7_32.jpg</t>
   </si>
   <si>
-    <t>ホロライブ ウエハースEXPO2024 Vol.01</t>
-  </si>
-  <si>
     <t>ホロライブインドネシア2期生</t>
   </si>
   <si>
@@ -2492,9 +2474,6 @@
     <t>waf-expo2024-vol1_41.jpg</t>
   </si>
   <si>
-    <t>ホロライブ ウエハースEXPO2024 Vol.02</t>
-  </si>
-  <si>
     <t>火威青</t>
   </si>
   <si>
@@ -2617,6 +2596,34 @@
   </si>
   <si>
     <t>waf-expo2024-vol2_37.jpg</t>
+  </si>
+  <si>
+    <t>ホロライブ ウエハース Vol.03</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ホロライブ ウエハース Vol.04</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ホロライブ ウエハース Vol.05</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ホロライブ ウエハース Vol.06</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ホロライブ ウエハース Vol.07</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ホロライブ ウエハース EXPO2024 Vol.01</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ホロライブ ウエハース EXPO2024 Vol.02</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -8745,7 +8752,7 @@
     </row>
     <row r="330" spans="1:6">
       <c r="A330" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>79</v>
@@ -8757,12 +8764,12 @@
         <v>2</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="331" spans="1:6">
       <c r="A331" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>81</v>
@@ -8774,12 +8781,12 @@
         <v>1</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="332" spans="1:6">
       <c r="A332" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>83</v>
@@ -8791,12 +8798,12 @@
         <v>2</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="333" spans="1:6">
       <c r="A333" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B333" s="2" t="s">
         <v>85</v>
@@ -8808,12 +8815,12 @@
         <v>6</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="334" spans="1:6">
       <c r="A334" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>87</v>
@@ -8825,12 +8832,12 @@
         <v>1</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="335" spans="1:6">
       <c r="A335" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>89</v>
@@ -8842,12 +8849,12 @@
         <v>1</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="336" spans="1:6">
       <c r="A336" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>91</v>
@@ -8859,12 +8866,12 @@
         <v>2</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="337" spans="1:6">
       <c r="A337" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>93</v>
@@ -8876,12 +8883,12 @@
         <v>7</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="338" spans="1:6">
       <c r="A338" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>95</v>
@@ -8893,12 +8900,12 @@
         <v>3</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="339" spans="1:6">
       <c r="A339" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>97</v>
@@ -8910,12 +8917,12 @@
         <v>4</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="340" spans="1:6">
       <c r="A340" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>99</v>
@@ -8927,12 +8934,12 @@
         <v>5</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="341" spans="1:6">
       <c r="A341" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>101</v>
@@ -8944,12 +8951,12 @@
         <v>2</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="342" spans="1:6">
       <c r="A342" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>103</v>
@@ -8961,12 +8968,12 @@
         <v>2</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="343" spans="1:6">
       <c r="A343" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>105</v>
@@ -8978,12 +8985,12 @@
         <v>5</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="344" spans="1:6">
       <c r="A344" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>107</v>
@@ -8995,12 +9002,12 @@
         <v>3</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="345" spans="1:6">
       <c r="A345" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>109</v>
@@ -9012,12 +9019,12 @@
         <v>1</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="346" spans="1:6">
       <c r="A346" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>111</v>
@@ -9029,12 +9036,12 @@
         <v>4</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="347" spans="1:6">
       <c r="A347" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>113</v>
@@ -9046,12 +9053,12 @@
         <v>3</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="348" spans="1:6">
       <c r="A348" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>115</v>
@@ -9063,12 +9070,12 @@
         <v>4</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="349" spans="1:6">
       <c r="A349" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B349" s="2" t="s">
         <v>117</v>
@@ -9080,12 +9087,12 @@
         <v>6</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="350" spans="1:6">
       <c r="A350" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>119</v>
@@ -9097,12 +9104,12 @@
         <v>0</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="351" spans="1:6">
       <c r="A351" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>121</v>
@@ -9114,12 +9121,12 @@
         <v>4</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="352" spans="1:6">
       <c r="A352" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>123</v>
@@ -9131,12 +9138,12 @@
         <v>3</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="353" spans="1:6">
       <c r="A353" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>125</v>
@@ -9148,12 +9155,12 @@
         <v>3</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="354" spans="1:6">
       <c r="A354" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>127</v>
@@ -9165,12 +9172,12 @@
         <v>0</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="355" spans="1:6">
       <c r="A355" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>129</v>
@@ -9182,12 +9189,12 @@
         <v>0</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="356" spans="1:6">
       <c r="A356" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B356" s="2" t="s">
         <v>131</v>
@@ -9199,12 +9206,12 @@
         <v>8</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="357" spans="1:6">
       <c r="A357" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>133</v>
@@ -9216,12 +9223,12 @@
         <v>2</v>
       </c>
       <c r="F357" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="358" spans="1:6">
       <c r="A358" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>135</v>
@@ -9233,12 +9240,12 @@
         <v>2</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="359" spans="1:6">
       <c r="A359" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>137</v>
@@ -9250,12 +9257,12 @@
         <v>3</v>
       </c>
       <c r="F359" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="360" spans="1:6">
       <c r="A360" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>139</v>
@@ -9267,12 +9274,12 @@
         <v>2</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="361" spans="1:6">
       <c r="A361" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>141</v>
@@ -9284,12 +9291,12 @@
         <v>3</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="362" spans="1:6">
       <c r="A362" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>143</v>
@@ -9301,12 +9308,12 @@
         <v>2</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="363" spans="1:6">
       <c r="A363" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>145</v>
@@ -9318,12 +9325,12 @@
         <v>1</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="364" spans="1:6">
       <c r="A364" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>147</v>
@@ -9335,12 +9342,12 @@
         <v>4</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="365" spans="1:6">
       <c r="A365" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>149</v>
@@ -9352,12 +9359,12 @@
         <v>3</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="366" spans="1:6">
       <c r="A366" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>151</v>
@@ -9369,12 +9376,12 @@
         <v>2</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="367" spans="1:6">
       <c r="A367" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>153</v>
@@ -9386,63 +9393,63 @@
         <v>3</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="368" spans="1:6">
       <c r="A368" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>155</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D368" s="2">
         <v>2</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="369" spans="1:6">
       <c r="A369" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>157</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D369" s="2">
         <v>2</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="370" spans="1:6">
       <c r="A370" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D370" s="2">
         <v>2</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="371" spans="1:6">
       <c r="A371" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>161</v>
@@ -9454,12 +9461,12 @@
         <v>2</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="372" spans="1:6">
       <c r="A372" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B372" s="2" t="s">
         <v>163</v>
@@ -9471,12 +9478,12 @@
         <v>2</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="373" spans="1:6">
       <c r="A373" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>501</v>
@@ -9488,12 +9495,12 @@
         <v>4</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="374" spans="1:6">
       <c r="A374" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>502</v>
@@ -9505,12 +9512,12 @@
         <v>4</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="375" spans="1:6">
       <c r="A375" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>503</v>
@@ -9522,12 +9529,12 @@
         <v>3</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="376" spans="1:6">
       <c r="A376" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B376" s="2" t="s">
         <v>504</v>
@@ -9539,12 +9546,12 @@
         <v>1</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="377" spans="1:6">
       <c r="A377" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B377" s="2" t="s">
         <v>505</v>
@@ -9556,12 +9563,12 @@
         <v>2</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="378" spans="1:6">
       <c r="A378" s="1" t="s">
-        <v>560</v>
+        <v>842</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>506</v>
@@ -9573,12 +9580,12 @@
         <v>3</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="379" spans="1:6">
       <c r="A379" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>79</v>
@@ -9590,12 +9597,12 @@
         <v>2</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="380" spans="1:6">
       <c r="A380" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B380" s="2" t="s">
         <v>81</v>
@@ -9607,12 +9614,12 @@
         <v>5</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="381" spans="1:6">
       <c r="A381" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B381" s="2" t="s">
         <v>83</v>
@@ -9624,12 +9631,12 @@
         <v>4</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="382" spans="1:6">
       <c r="A382" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B382" s="2" t="s">
         <v>85</v>
@@ -9641,12 +9648,12 @@
         <v>5</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="383" spans="1:6">
       <c r="A383" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B383" s="2" t="s">
         <v>87</v>
@@ -9658,12 +9665,12 @@
         <v>5</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="384" spans="1:6">
       <c r="A384" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B384" s="2" t="s">
         <v>89</v>
@@ -9675,12 +9682,12 @@
         <v>7</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="385" spans="1:6">
       <c r="A385" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>91</v>
@@ -9692,12 +9699,12 @@
         <v>2</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="386" spans="1:6">
       <c r="A386" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>93</v>
@@ -9709,12 +9716,12 @@
         <v>2</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="387" spans="1:6">
       <c r="A387" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B387" s="2" t="s">
         <v>95</v>
@@ -9726,12 +9733,12 @@
         <v>3</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="388" spans="1:6">
       <c r="A388" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B388" s="2" t="s">
         <v>97</v>
@@ -9743,12 +9750,12 @@
         <v>2</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="389" spans="1:6">
       <c r="A389" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B389" s="2" t="s">
         <v>99</v>
@@ -9760,12 +9767,12 @@
         <v>7</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="390" spans="1:6">
       <c r="A390" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B390" s="2" t="s">
         <v>101</v>
@@ -9777,12 +9784,12 @@
         <v>4</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="391" spans="1:6">
       <c r="A391" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B391" s="2" t="s">
         <v>103</v>
@@ -9794,12 +9801,12 @@
         <v>6</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="392" spans="1:6">
       <c r="A392" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B392" s="2" t="s">
         <v>105</v>
@@ -9811,12 +9818,12 @@
         <v>6</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="393" spans="1:6">
       <c r="A393" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B393" s="2" t="s">
         <v>107</v>
@@ -9828,12 +9835,12 @@
         <v>0</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="394" spans="1:6">
       <c r="A394" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B394" s="2" t="s">
         <v>109</v>
@@ -9845,12 +9852,12 @@
         <v>3</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="395" spans="1:6">
       <c r="A395" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B395" s="2" t="s">
         <v>111</v>
@@ -9862,12 +9869,12 @@
         <v>5</v>
       </c>
       <c r="F395" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="396" spans="1:6">
       <c r="A396" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B396" s="2" t="s">
         <v>113</v>
@@ -9879,12 +9886,12 @@
         <v>4</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="397" spans="1:6">
       <c r="A397" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B397" s="2" t="s">
         <v>115</v>
@@ -9896,12 +9903,12 @@
         <v>8</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="398" spans="1:6">
       <c r="A398" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B398" s="2" t="s">
         <v>117</v>
@@ -9913,12 +9920,12 @@
         <v>2</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="399" spans="1:6">
       <c r="A399" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B399" s="2" t="s">
         <v>119</v>
@@ -9930,12 +9937,12 @@
         <v>3</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="400" spans="1:6">
       <c r="A400" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B400" s="2" t="s">
         <v>121</v>
@@ -9947,12 +9954,12 @@
         <v>4</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="401" spans="1:6">
       <c r="A401" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>123</v>
@@ -9964,12 +9971,12 @@
         <v>1</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="402" spans="1:6">
       <c r="A402" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B402" s="2" t="s">
         <v>125</v>
@@ -9981,12 +9988,12 @@
         <v>3</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="403" spans="1:6">
       <c r="A403" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B403" s="2" t="s">
         <v>127</v>
@@ -9998,12 +10005,12 @@
         <v>5</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="404" spans="1:6">
       <c r="A404" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B404" s="2" t="s">
         <v>129</v>
@@ -10015,12 +10022,12 @@
         <v>2</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="405" spans="1:6">
       <c r="A405" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B405" s="2" t="s">
         <v>131</v>
@@ -10032,80 +10039,80 @@
         <v>2</v>
       </c>
       <c r="F405" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="406" spans="1:6">
       <c r="A406" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B406" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C406" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D406" s="2">
         <v>2</v>
       </c>
       <c r="F406" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="407" spans="1:6">
       <c r="A407" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B407" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D407" s="2">
         <v>2</v>
       </c>
       <c r="F407" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="408" spans="1:6">
       <c r="A408" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B408" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C408" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D408" s="2">
         <v>2</v>
       </c>
       <c r="F408" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="409" spans="1:6">
       <c r="A409" s="1" t="s">
-        <v>613</v>
+        <v>843</v>
       </c>
       <c r="B409" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C409" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D409" s="2">
         <v>4</v>
       </c>
       <c r="F409" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="410" spans="1:6">
       <c r="A410" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B410" s="2" t="s">
         <v>79</v>
@@ -10117,12 +10124,12 @@
         <v>3</v>
       </c>
       <c r="F410" s="1" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="411" spans="1:6">
       <c r="A411" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B411" s="2" t="s">
         <v>81</v>
@@ -10134,12 +10141,12 @@
         <v>3</v>
       </c>
       <c r="F411" s="1" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
     </row>
     <row r="412" spans="1:6">
       <c r="A412" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B412" s="2" t="s">
         <v>83</v>
@@ -10151,12 +10158,12 @@
         <v>2</v>
       </c>
       <c r="F412" s="1" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="413" spans="1:6">
       <c r="A413" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B413" s="2" t="s">
         <v>85</v>
@@ -10168,12 +10175,12 @@
         <v>2</v>
       </c>
       <c r="F413" s="1" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
     </row>
     <row r="414" spans="1:6">
       <c r="A414" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B414" s="2" t="s">
         <v>87</v>
@@ -10185,12 +10192,12 @@
         <v>3</v>
       </c>
       <c r="F414" s="1" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="415" spans="1:6">
       <c r="A415" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B415" s="2" t="s">
         <v>89</v>
@@ -10202,12 +10209,12 @@
         <v>3</v>
       </c>
       <c r="F415" s="1" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="416" spans="1:6">
       <c r="A416" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B416" s="2" t="s">
         <v>91</v>
@@ -10219,12 +10226,12 @@
         <v>2</v>
       </c>
       <c r="F416" s="1" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
     </row>
     <row r="417" spans="1:6">
       <c r="A417" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B417" s="2" t="s">
         <v>93</v>
@@ -10236,12 +10243,12 @@
         <v>2</v>
       </c>
       <c r="F417" s="1" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
     </row>
     <row r="418" spans="1:6">
       <c r="A418" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B418" s="2" t="s">
         <v>95</v>
@@ -10253,12 +10260,12 @@
         <v>1</v>
       </c>
       <c r="F418" s="1" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="419" spans="1:6">
       <c r="A419" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B419" s="2" t="s">
         <v>97</v>
@@ -10270,12 +10277,12 @@
         <v>5</v>
       </c>
       <c r="F419" s="1" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
     </row>
     <row r="420" spans="1:6">
       <c r="A420" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B420" s="2" t="s">
         <v>99</v>
@@ -10287,12 +10294,12 @@
         <v>3</v>
       </c>
       <c r="F420" s="1" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
     </row>
     <row r="421" spans="1:6">
       <c r="A421" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B421" s="2" t="s">
         <v>101</v>
@@ -10304,12 +10311,12 @@
         <v>2</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
     </row>
     <row r="422" spans="1:6">
       <c r="A422" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B422" s="2" t="s">
         <v>103</v>
@@ -10321,12 +10328,12 @@
         <v>1</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
     </row>
     <row r="423" spans="1:6">
       <c r="A423" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B423" s="2" t="s">
         <v>105</v>
@@ -10338,12 +10345,12 @@
         <v>2</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="424" spans="1:6">
       <c r="A424" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B424" s="2" t="s">
         <v>107</v>
@@ -10355,12 +10362,12 @@
         <v>2</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="425" spans="1:6">
       <c r="A425" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>109</v>
@@ -10372,301 +10379,301 @@
         <v>1</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="426" spans="1:6">
       <c r="A426" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B426" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D426" s="2">
         <v>2</v>
       </c>
       <c r="F426" s="1" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="427" spans="1:6">
       <c r="A427" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B427" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D427" s="2">
         <v>2</v>
       </c>
       <c r="F427" s="1" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="428" spans="1:6">
       <c r="A428" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B428" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D428" s="2">
         <v>2</v>
       </c>
       <c r="F428" s="1" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="429" spans="1:6">
       <c r="A429" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B429" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="D429" s="2">
         <v>3</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
     </row>
     <row r="430" spans="1:6">
       <c r="A430" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B430" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="D430" s="2">
         <v>2</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="431" spans="1:6">
       <c r="A431" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B431" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C431" s="1" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="D431" s="2">
         <v>3</v>
       </c>
       <c r="F431" s="1" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
     </row>
     <row r="432" spans="1:6">
       <c r="A432" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B432" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C432" s="1" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="D432" s="2">
         <v>2</v>
       </c>
       <c r="F432" s="1" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="433" spans="1:6">
       <c r="A433" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B433" s="2" t="s">
         <v>125</v>
       </c>
       <c r="C433" s="1" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="D433" s="2">
         <v>2</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
     </row>
     <row r="434" spans="1:6">
       <c r="A434" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B434" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C434" s="1" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="D434" s="2">
         <v>1</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
     </row>
     <row r="435" spans="1:6">
       <c r="A435" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B435" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="D435" s="2">
         <v>3</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
     </row>
     <row r="436" spans="1:6">
       <c r="A436" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B436" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C436" s="1" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="D436" s="2">
         <v>1</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="437" spans="1:6">
       <c r="A437" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B437" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C437" s="1" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="D437" s="2">
         <v>2</v>
       </c>
       <c r="F437" s="1" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="438" spans="1:6">
       <c r="A438" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B438" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C438" s="1" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="D438" s="2">
         <v>1</v>
       </c>
       <c r="F438" s="1" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="439" spans="1:6">
       <c r="A439" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B439" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C439" s="1" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="D439" s="2">
         <v>1</v>
       </c>
       <c r="F439" s="1" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="440" spans="1:6">
       <c r="A440" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C440" s="1" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="D440" s="2">
         <v>3</v>
       </c>
       <c r="F440" s="1" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
     </row>
     <row r="441" spans="1:6">
       <c r="A441" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B441" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C441" s="1" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="D441" s="2">
         <v>1</v>
       </c>
       <c r="F441" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="442" spans="1:6">
       <c r="A442" s="1" t="s">
-        <v>649</v>
+        <v>844</v>
       </c>
       <c r="B442" s="2" t="s">
         <v>143</v>
       </c>
       <c r="C442" s="1" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="D442" s="2">
         <v>2</v>
       </c>
       <c r="F442" s="1" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
     </row>
     <row r="443" spans="1:6">
       <c r="A443" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B443" s="2" t="s">
         <v>79</v>
@@ -10674,13 +10681,16 @@
       <c r="C443" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="D443" s="2">
+        <v>3</v>
+      </c>
       <c r="F443" s="1" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
     </row>
     <row r="444" spans="1:6">
       <c r="A444" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B444" s="2" t="s">
         <v>81</v>
@@ -10688,13 +10698,16 @@
       <c r="C444" s="1" t="s">
         <v>57</v>
       </c>
+      <c r="D444" s="2">
+        <v>2</v>
+      </c>
       <c r="F444" s="1" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
     </row>
     <row r="445" spans="1:6">
       <c r="A445" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>83</v>
@@ -10702,13 +10715,16 @@
       <c r="C445" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="D445" s="2">
+        <v>3</v>
+      </c>
       <c r="F445" s="1" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
     </row>
     <row r="446" spans="1:6">
       <c r="A446" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B446" s="2" t="s">
         <v>85</v>
@@ -10716,13 +10732,16 @@
       <c r="C446" s="1" t="s">
         <v>59</v>
       </c>
+      <c r="D446" s="2">
+        <v>3</v>
+      </c>
       <c r="F446" s="1" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
     </row>
     <row r="447" spans="1:6">
       <c r="A447" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B447" s="2" t="s">
         <v>87</v>
@@ -10730,13 +10749,16 @@
       <c r="C447" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="D447" s="2">
+        <v>2</v>
+      </c>
       <c r="F447" s="1" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
     </row>
     <row r="448" spans="1:6">
       <c r="A448" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B448" s="2" t="s">
         <v>89</v>
@@ -10744,13 +10766,16 @@
       <c r="C448" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="D448" s="2">
+        <v>3</v>
+      </c>
       <c r="F448" s="1" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
     </row>
     <row r="449" spans="1:6">
       <c r="A449" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B449" s="2" t="s">
         <v>91</v>
@@ -10758,13 +10783,16 @@
       <c r="C449" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="D449" s="2">
+        <v>2</v>
+      </c>
       <c r="F449" s="1" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
     </row>
     <row r="450" spans="1:6">
       <c r="A450" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B450" s="2" t="s">
         <v>93</v>
@@ -10772,13 +10800,16 @@
       <c r="C450" s="1" t="s">
         <v>63</v>
       </c>
+      <c r="D450" s="2">
+        <v>1</v>
+      </c>
       <c r="F450" s="1" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
     </row>
     <row r="451" spans="1:6">
       <c r="A451" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B451" s="2" t="s">
         <v>95</v>
@@ -10786,13 +10817,16 @@
       <c r="C451" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D451" s="2">
+        <v>2</v>
+      </c>
       <c r="F451" s="1" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
     </row>
     <row r="452" spans="1:6">
       <c r="A452" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B452" s="2" t="s">
         <v>97</v>
@@ -10800,13 +10834,16 @@
       <c r="C452" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="D452" s="2">
+        <v>2</v>
+      </c>
       <c r="F452" s="1" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
     </row>
     <row r="453" spans="1:6">
       <c r="A453" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B453" s="2" t="s">
         <v>99</v>
@@ -10814,13 +10851,16 @@
       <c r="C453" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="D453" s="2">
+        <v>2</v>
+      </c>
       <c r="F453" s="1" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
     </row>
     <row r="454" spans="1:6">
       <c r="A454" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B454" s="2" t="s">
         <v>101</v>
@@ -10828,13 +10868,16 @@
       <c r="C454" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D454" s="2">
+        <v>2</v>
+      </c>
       <c r="F454" s="1" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
     </row>
     <row r="455" spans="1:6">
       <c r="A455" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B455" s="2" t="s">
         <v>103</v>
@@ -10842,13 +10885,16 @@
       <c r="C455" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D455" s="2">
+        <v>3</v>
+      </c>
       <c r="F455" s="1" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
     </row>
     <row r="456" spans="1:6">
       <c r="A456" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B456" s="2" t="s">
         <v>105</v>
@@ -10856,13 +10902,16 @@
       <c r="C456" s="1" t="s">
         <v>66</v>
       </c>
+      <c r="D456" s="2">
+        <v>4</v>
+      </c>
       <c r="F456" s="1" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
     </row>
     <row r="457" spans="1:6">
       <c r="A457" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B457" s="2" t="s">
         <v>107</v>
@@ -10870,13 +10919,16 @@
       <c r="C457" s="1" t="s">
         <v>148</v>
       </c>
+      <c r="D457" s="2">
+        <v>1</v>
+      </c>
       <c r="F457" s="1" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
     </row>
     <row r="458" spans="1:6">
       <c r="A458" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B458" s="2" t="s">
         <v>109</v>
@@ -10884,13 +10936,16 @@
       <c r="C458" s="1" t="s">
         <v>202</v>
       </c>
+      <c r="D458" s="2">
+        <v>1</v>
+      </c>
       <c r="F458" s="1" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
     </row>
     <row r="459" spans="1:6">
       <c r="A459" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B459" s="2" t="s">
         <v>111</v>
@@ -10898,13 +10953,16 @@
       <c r="C459" s="1" t="s">
         <v>150</v>
       </c>
+      <c r="D459" s="2">
+        <v>2</v>
+      </c>
       <c r="F459" s="1" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
     </row>
     <row r="460" spans="1:6">
       <c r="A460" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B460" s="2" t="s">
         <v>113</v>
@@ -10912,13 +10970,16 @@
       <c r="C460" s="1" t="s">
         <v>203</v>
       </c>
+      <c r="D460" s="2">
+        <v>3</v>
+      </c>
       <c r="F460" s="1" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
     </row>
     <row r="461" spans="1:6">
       <c r="A461" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B461" s="2" t="s">
         <v>115</v>
@@ -10926,13 +10987,16 @@
       <c r="C461" s="1" t="s">
         <v>152</v>
       </c>
+      <c r="D461" s="2">
+        <v>1</v>
+      </c>
       <c r="F461" s="1" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
     </row>
     <row r="462" spans="1:6">
       <c r="A462" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B462" s="2" t="s">
         <v>117</v>
@@ -10940,13 +11004,16 @@
       <c r="C462" s="1" t="s">
         <v>204</v>
       </c>
+      <c r="D462" s="2">
+        <v>3</v>
+      </c>
       <c r="F462" s="1" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
     </row>
     <row r="463" spans="1:6">
       <c r="A463" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B463" s="2" t="s">
         <v>119</v>
@@ -10954,13 +11021,16 @@
       <c r="C463" s="1" t="s">
         <v>154</v>
       </c>
+      <c r="D463" s="2">
+        <v>2</v>
+      </c>
       <c r="F463" s="1" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
     </row>
     <row r="464" spans="1:6">
       <c r="A464" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B464" s="2" t="s">
         <v>121</v>
@@ -10968,13 +11038,16 @@
       <c r="C464" s="1" t="s">
         <v>156</v>
       </c>
+      <c r="D464" s="2">
+        <v>2</v>
+      </c>
       <c r="F464" s="1" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
     </row>
     <row r="465" spans="1:6">
       <c r="A465" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B465" s="2" t="s">
         <v>123</v>
@@ -10982,13 +11055,16 @@
       <c r="C465" s="1" t="s">
         <v>158</v>
       </c>
+      <c r="D465" s="2">
+        <v>1</v>
+      </c>
       <c r="F465" s="1" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
     </row>
     <row r="466" spans="1:6">
       <c r="A466" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B466" s="2" t="s">
         <v>125</v>
@@ -10996,13 +11072,16 @@
       <c r="C466" s="1" t="s">
         <v>160</v>
       </c>
+      <c r="D466" s="2">
+        <v>1</v>
+      </c>
       <c r="F466" s="1" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
     </row>
     <row r="467" spans="1:6">
       <c r="A467" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B467" s="2" t="s">
         <v>127</v>
@@ -11010,13 +11089,16 @@
       <c r="C467" s="1" t="s">
         <v>207</v>
       </c>
+      <c r="D467" s="2">
+        <v>2</v>
+      </c>
       <c r="F467" s="1" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
     </row>
     <row r="468" spans="1:6">
       <c r="A468" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B468" s="2" t="s">
         <v>129</v>
@@ -11024,69 +11106,84 @@
       <c r="C468" s="1" t="s">
         <v>164</v>
       </c>
+      <c r="D468" s="2">
+        <v>2</v>
+      </c>
       <c r="F468" s="1" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
     </row>
     <row r="469" spans="1:6">
       <c r="A469" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B469" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C469" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
+      </c>
+      <c r="D469" s="2">
+        <v>2</v>
       </c>
       <c r="F469" s="1" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
     </row>
     <row r="470" spans="1:6">
       <c r="A470" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B470" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C470" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
+      </c>
+      <c r="D470" s="2">
+        <v>3</v>
       </c>
       <c r="F470" s="1" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
     </row>
     <row r="471" spans="1:6">
       <c r="A471" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B471" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C471" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
+      </c>
+      <c r="D471" s="2">
+        <v>3</v>
       </c>
       <c r="F471" s="1" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
     </row>
     <row r="472" spans="1:6">
       <c r="A472" s="1" t="s">
-        <v>697</v>
+        <v>845</v>
       </c>
       <c r="B472" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C472" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
+      </c>
+      <c r="D472" s="2">
+        <v>1</v>
       </c>
       <c r="F472" s="1" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
     </row>
     <row r="473" spans="1:6">
       <c r="A473" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B473" s="2" t="s">
         <v>79</v>
@@ -11095,12 +11192,12 @@
         <v>67</v>
       </c>
       <c r="F473" s="1" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
     </row>
     <row r="474" spans="1:6">
       <c r="A474" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B474" s="2" t="s">
         <v>81</v>
@@ -11109,12 +11206,12 @@
         <v>68</v>
       </c>
       <c r="F474" s="1" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
     </row>
     <row r="475" spans="1:6">
       <c r="A475" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B475" s="2" t="s">
         <v>83</v>
@@ -11123,12 +11220,12 @@
         <v>47</v>
       </c>
       <c r="F475" s="1" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
     </row>
     <row r="476" spans="1:6">
       <c r="A476" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B476" s="2" t="s">
         <v>85</v>
@@ -11137,12 +11234,12 @@
         <v>48</v>
       </c>
       <c r="F476" s="1" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
     </row>
     <row r="477" spans="1:6">
       <c r="A477" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B477" s="2" t="s">
         <v>87</v>
@@ -11151,12 +11248,12 @@
         <v>49</v>
       </c>
       <c r="F477" s="1" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
     </row>
     <row r="478" spans="1:6">
       <c r="A478" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B478" s="2" t="s">
         <v>89</v>
@@ -11165,12 +11262,12 @@
         <v>50</v>
       </c>
       <c r="F478" s="1" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
     </row>
     <row r="479" spans="1:6">
       <c r="A479" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B479" s="2" t="s">
         <v>91</v>
@@ -11179,12 +11276,12 @@
         <v>70</v>
       </c>
       <c r="F479" s="1" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
     </row>
     <row r="480" spans="1:6">
       <c r="A480" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B480" s="2" t="s">
         <v>93</v>
@@ -11193,12 +11290,12 @@
         <v>51</v>
       </c>
       <c r="F480" s="1" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
     </row>
     <row r="481" spans="1:6">
       <c r="A481" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B481" s="2" t="s">
         <v>95</v>
@@ -11207,12 +11304,12 @@
         <v>71</v>
       </c>
       <c r="F481" s="1" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
     </row>
     <row r="482" spans="1:6">
       <c r="A482" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B482" s="2" t="s">
         <v>97</v>
@@ -11221,12 +11318,12 @@
         <v>52</v>
       </c>
       <c r="F482" s="1" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
     </row>
     <row r="483" spans="1:6">
       <c r="A483" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B483" s="2" t="s">
         <v>99</v>
@@ -11235,12 +11332,12 @@
         <v>72</v>
       </c>
       <c r="F483" s="1" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
     </row>
     <row r="484" spans="1:6">
       <c r="A484" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B484" s="2" t="s">
         <v>101</v>
@@ -11249,12 +11346,12 @@
         <v>53</v>
       </c>
       <c r="F484" s="1" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
     </row>
     <row r="485" spans="1:6">
       <c r="A485" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B485" s="2" t="s">
         <v>103</v>
@@ -11263,12 +11360,12 @@
         <v>73</v>
       </c>
       <c r="F485" s="1" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
     </row>
     <row r="486" spans="1:6">
       <c r="A486" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B486" s="2" t="s">
         <v>105</v>
@@ -11277,12 +11374,12 @@
         <v>54</v>
       </c>
       <c r="F486" s="1" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
     </row>
     <row r="487" spans="1:6">
       <c r="A487" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B487" s="2" t="s">
         <v>107</v>
@@ -11291,250 +11388,250 @@
         <v>55</v>
       </c>
       <c r="F487" s="1" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
     </row>
     <row r="488" spans="1:6">
       <c r="A488" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B488" s="2" t="s">
         <v>109</v>
       </c>
       <c r="C488" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F488" s="1" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
     </row>
     <row r="489" spans="1:6">
       <c r="A489" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B489" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C489" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="F489" s="1" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
     </row>
     <row r="490" spans="1:6">
       <c r="A490" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B490" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C490" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="F490" s="1" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
     </row>
     <row r="491" spans="1:6">
       <c r="A491" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B491" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C491" s="1" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="F491" s="1" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
     </row>
     <row r="492" spans="1:6">
       <c r="A492" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B492" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C492" s="1" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="F492" s="1" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
     </row>
     <row r="493" spans="1:6">
       <c r="A493" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B493" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C493" s="1" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="F493" s="1" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
     </row>
     <row r="494" spans="1:6">
       <c r="A494" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B494" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C494" s="1" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="F494" s="1" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
     </row>
     <row r="495" spans="1:6">
       <c r="A495" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B495" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C495" s="1" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="F495" s="1" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
     </row>
     <row r="496" spans="1:6">
       <c r="A496" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B496" s="2" t="s">
         <v>125</v>
       </c>
       <c r="C496" s="1" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="F496" s="1" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
     </row>
     <row r="497" spans="1:6">
       <c r="A497" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C497" s="1" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="F497" s="1" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
     </row>
     <row r="498" spans="1:6">
       <c r="A498" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B498" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C498" s="1" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="F498" s="1" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
     </row>
     <row r="499" spans="1:6">
       <c r="A499" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B499" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C499" s="1" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="F499" s="1" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
     </row>
     <row r="500" spans="1:6">
       <c r="A500" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B500" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C500" s="1" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="F500" s="1" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
     </row>
     <row r="501" spans="1:6">
       <c r="A501" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B501" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C501" s="1" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="F501" s="1" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
     </row>
     <row r="502" spans="1:6">
       <c r="A502" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C502" s="1" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="F502" s="1" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
     </row>
     <row r="503" spans="1:6">
       <c r="A503" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B503" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C503" s="1" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="F503" s="1" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
     </row>
     <row r="504" spans="1:6">
       <c r="A504" s="1" t="s">
-        <v>698</v>
+        <v>846</v>
       </c>
       <c r="B504" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C504" s="1" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="F504" s="1" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
     </row>
     <row r="505" spans="1:6">
       <c r="A505" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B505" s="2" t="s">
         <v>79</v>
@@ -11546,12 +11643,12 @@
         <v>5</v>
       </c>
       <c r="F505" s="1" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
     </row>
     <row r="506" spans="1:6">
       <c r="A506" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B506" s="2" t="s">
         <v>81</v>
@@ -11563,12 +11660,12 @@
         <v>5</v>
       </c>
       <c r="F506" s="1" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
     </row>
     <row r="507" spans="1:6">
       <c r="A507" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B507" s="2" t="s">
         <v>83</v>
@@ -11580,12 +11677,12 @@
         <v>1</v>
       </c>
       <c r="F507" s="1" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
     </row>
     <row r="508" spans="1:6">
       <c r="A508" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B508" s="2" t="s">
         <v>85</v>
@@ -11597,12 +11694,12 @@
         <v>1</v>
       </c>
       <c r="F508" s="1" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
     </row>
     <row r="509" spans="1:6">
       <c r="A509" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B509" s="2" t="s">
         <v>87</v>
@@ -11614,12 +11711,12 @@
         <v>4</v>
       </c>
       <c r="F509" s="1" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
     </row>
     <row r="510" spans="1:6">
       <c r="A510" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B510" s="2" t="s">
         <v>89</v>
@@ -11631,12 +11728,12 @@
         <v>4</v>
       </c>
       <c r="F510" s="1" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
     </row>
     <row r="511" spans="1:6">
       <c r="A511" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B511" s="2" t="s">
         <v>91</v>
@@ -11648,12 +11745,12 @@
         <v>3</v>
       </c>
       <c r="F511" s="1" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
     </row>
     <row r="512" spans="1:6">
       <c r="A512" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B512" s="2" t="s">
         <v>93</v>
@@ -11668,12 +11765,12 @@
         <v>1</v>
       </c>
       <c r="F512" s="1" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
     </row>
     <row r="513" spans="1:6">
       <c r="A513" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B513" s="2" t="s">
         <v>95</v>
@@ -11685,12 +11782,12 @@
         <v>0</v>
       </c>
       <c r="F513" s="1" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
     </row>
     <row r="514" spans="1:6">
       <c r="A514" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B514" s="2" t="s">
         <v>97</v>
@@ -11702,12 +11799,12 @@
         <v>0</v>
       </c>
       <c r="F514" s="1" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
     </row>
     <row r="515" spans="1:6">
       <c r="A515" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B515" s="2" t="s">
         <v>99</v>
@@ -11719,12 +11816,12 @@
         <v>2</v>
       </c>
       <c r="F515" s="1" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
     </row>
     <row r="516" spans="1:6">
       <c r="A516" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B516" s="2" t="s">
         <v>101</v>
@@ -11736,12 +11833,12 @@
         <v>3</v>
       </c>
       <c r="F516" s="1" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
     </row>
     <row r="517" spans="1:6">
       <c r="A517" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B517" s="2" t="s">
         <v>103</v>
@@ -11753,12 +11850,12 @@
         <v>2</v>
       </c>
       <c r="F517" s="1" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
     </row>
     <row r="518" spans="1:6">
       <c r="A518" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B518" s="2" t="s">
         <v>105</v>
@@ -11770,12 +11867,12 @@
         <v>4</v>
       </c>
       <c r="F518" s="1" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
     </row>
     <row r="519" spans="1:6">
       <c r="A519" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B519" s="2" t="s">
         <v>107</v>
@@ -11787,12 +11884,12 @@
         <v>3</v>
       </c>
       <c r="F519" s="1" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
     </row>
     <row r="520" spans="1:6">
       <c r="A520" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B520" s="2" t="s">
         <v>109</v>
@@ -11804,12 +11901,12 @@
         <v>2</v>
       </c>
       <c r="F520" s="1" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
     </row>
     <row r="521" spans="1:6">
       <c r="A521" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B521" s="2" t="s">
         <v>111</v>
@@ -11821,12 +11918,12 @@
         <v>3</v>
       </c>
       <c r="F521" s="1" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
     </row>
     <row r="522" spans="1:6">
       <c r="A522" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B522" s="2" t="s">
         <v>113</v>
@@ -11838,12 +11935,12 @@
         <v>1</v>
       </c>
       <c r="F522" s="1" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
     </row>
     <row r="523" spans="1:6">
       <c r="A523" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B523" s="2" t="s">
         <v>115</v>
@@ -11855,12 +11952,12 @@
         <v>1</v>
       </c>
       <c r="F523" s="1" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
     </row>
     <row r="524" spans="1:6">
       <c r="A524" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B524" s="2" t="s">
         <v>117</v>
@@ -11872,63 +11969,63 @@
         <v>4</v>
       </c>
       <c r="F524" s="1" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
     </row>
     <row r="525" spans="1:6">
       <c r="A525" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B525" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C525" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D525" s="2">
         <v>1</v>
       </c>
       <c r="F525" s="1" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
     </row>
     <row r="526" spans="1:6">
       <c r="A526" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B526" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C526" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D526" s="2">
         <v>3</v>
       </c>
       <c r="F526" s="1" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
     </row>
     <row r="527" spans="1:6">
       <c r="A527" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B527" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C527" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D527" s="2">
         <v>0</v>
       </c>
       <c r="F527" s="1" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
     </row>
     <row r="528" spans="1:6">
       <c r="A528" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B528" s="2" t="s">
         <v>125</v>
@@ -11940,12 +12037,12 @@
         <v>1</v>
       </c>
       <c r="F528" s="1" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
     </row>
     <row r="529" spans="1:6">
       <c r="A529" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B529" s="2" t="s">
         <v>127</v>
@@ -11957,12 +12054,12 @@
         <v>7</v>
       </c>
       <c r="F529" s="1" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
     </row>
     <row r="530" spans="1:6">
       <c r="A530" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>129</v>
@@ -11974,12 +12071,12 @@
         <v>1</v>
       </c>
       <c r="F530" s="1" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
     </row>
     <row r="531" spans="1:6">
       <c r="A531" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B531" s="2" t="s">
         <v>131</v>
@@ -11991,12 +12088,12 @@
         <v>3</v>
       </c>
       <c r="F531" s="1" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
     </row>
     <row r="532" spans="1:6">
       <c r="A532" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B532" s="2" t="s">
         <v>133</v>
@@ -12008,97 +12105,97 @@
         <v>4</v>
       </c>
       <c r="F532" s="1" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
     </row>
     <row r="533" spans="1:6">
       <c r="A533" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B533" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C533" s="1" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="D533" s="2">
         <v>1</v>
       </c>
       <c r="F533" s="1" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
     </row>
     <row r="534" spans="1:6">
       <c r="A534" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B534" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C534" s="1" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="D534" s="2">
         <v>1</v>
       </c>
       <c r="F534" s="1" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
     </row>
     <row r="535" spans="1:6">
       <c r="A535" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B535" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C535" s="1" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="D535" s="2">
         <v>0</v>
       </c>
       <c r="F535" s="1" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
     </row>
     <row r="536" spans="1:6">
       <c r="A536" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B536" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C536" s="1" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="D536" s="2">
         <v>0</v>
       </c>
       <c r="F536" s="1" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
     </row>
     <row r="537" spans="1:6">
       <c r="A537" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B537" s="2" t="s">
         <v>143</v>
       </c>
       <c r="C537" s="1" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="D537" s="2">
         <v>2</v>
       </c>
       <c r="F537" s="1" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
     </row>
     <row r="538" spans="1:6">
       <c r="A538" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B538" s="2" t="s">
         <v>145</v>
@@ -12110,12 +12207,12 @@
         <v>2</v>
       </c>
       <c r="F538" s="1" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
     </row>
     <row r="539" spans="1:6">
       <c r="A539" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B539" s="2" t="s">
         <v>147</v>
@@ -12127,12 +12224,12 @@
         <v>0</v>
       </c>
       <c r="F539" s="1" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
     </row>
     <row r="540" spans="1:6">
       <c r="A540" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B540" s="2" t="s">
         <v>149</v>
@@ -12144,12 +12241,12 @@
         <v>1</v>
       </c>
       <c r="F540" s="1" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
     </row>
     <row r="541" spans="1:6">
       <c r="A541" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B541" s="2" t="s">
         <v>151</v>
@@ -12161,80 +12258,80 @@
         <v>0</v>
       </c>
       <c r="F541" s="1" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
     </row>
     <row r="542" spans="1:6">
       <c r="A542" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B542" s="2" t="s">
         <v>153</v>
       </c>
       <c r="C542" s="1" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="D542" s="2">
         <v>4</v>
       </c>
       <c r="F542" s="1" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
     </row>
     <row r="543" spans="1:6">
       <c r="A543" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B543" s="2" t="s">
         <v>155</v>
       </c>
       <c r="C543" s="1" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="D543" s="2">
         <v>3</v>
       </c>
       <c r="F543" s="1" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
     </row>
     <row r="544" spans="1:6">
       <c r="A544" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B544" s="2" t="s">
         <v>157</v>
       </c>
       <c r="C544" s="1" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="D544" s="2">
         <v>0</v>
       </c>
       <c r="F544" s="1" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
     </row>
     <row r="545" spans="1:6">
       <c r="A545" s="1" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="B545" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C545" s="1" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="D545" s="2">
         <v>1</v>
       </c>
       <c r="F545" s="1" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
     </row>
     <row r="546" spans="1:6">
       <c r="A546" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B546" s="2" t="s">
         <v>79</v>
@@ -12246,12 +12343,12 @@
         <v>1</v>
       </c>
       <c r="F546" s="1" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
     </row>
     <row r="547" spans="1:6">
       <c r="A547" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B547" s="2" t="s">
         <v>81</v>
@@ -12263,12 +12360,12 @@
         <v>1</v>
       </c>
       <c r="F547" s="1" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
     </row>
     <row r="548" spans="1:6">
       <c r="A548" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B548" s="2" t="s">
         <v>83</v>
@@ -12280,12 +12377,12 @@
         <v>3</v>
       </c>
       <c r="F548" s="1" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
     </row>
     <row r="549" spans="1:6">
       <c r="A549" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B549" s="2" t="s">
         <v>85</v>
@@ -12297,12 +12394,12 @@
         <v>0</v>
       </c>
       <c r="F549" s="1" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
     </row>
     <row r="550" spans="1:6">
       <c r="A550" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B550" s="2" t="s">
         <v>87</v>
@@ -12314,12 +12411,12 @@
         <v>0</v>
       </c>
       <c r="F550" s="1" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
     </row>
     <row r="551" spans="1:6">
       <c r="A551" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B551" s="2" t="s">
         <v>89</v>
@@ -12331,12 +12428,12 @@
         <v>1</v>
       </c>
       <c r="F551" s="1" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
     </row>
     <row r="552" spans="1:6">
       <c r="A552" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B552" s="2" t="s">
         <v>91</v>
@@ -12348,12 +12445,12 @@
         <v>2</v>
       </c>
       <c r="F552" s="1" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
     </row>
     <row r="553" spans="1:6">
       <c r="A553" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B553" s="2" t="s">
         <v>93</v>
@@ -12365,12 +12462,12 @@
         <v>0</v>
       </c>
       <c r="F553" s="1" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
     </row>
     <row r="554" spans="1:6">
       <c r="A554" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B554" s="2" t="s">
         <v>95</v>
@@ -12382,12 +12479,12 @@
         <v>2</v>
       </c>
       <c r="F554" s="1" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
     </row>
     <row r="555" spans="1:6">
       <c r="A555" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B555" s="2" t="s">
         <v>97</v>
@@ -12399,12 +12496,12 @@
         <v>1</v>
       </c>
       <c r="F555" s="1" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
     </row>
     <row r="556" spans="1:6">
       <c r="A556" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B556" s="2" t="s">
         <v>99</v>
@@ -12416,12 +12513,12 @@
         <v>0</v>
       </c>
       <c r="F556" s="1" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
     </row>
     <row r="557" spans="1:6">
       <c r="A557" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B557" s="2" t="s">
         <v>101</v>
@@ -12433,12 +12530,12 @@
         <v>1</v>
       </c>
       <c r="F557" s="1" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
     </row>
     <row r="558" spans="1:6">
       <c r="A558" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B558" s="2" t="s">
         <v>103</v>
@@ -12450,12 +12547,12 @@
         <v>3</v>
       </c>
       <c r="F558" s="1" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
     </row>
     <row r="559" spans="1:6">
       <c r="A559" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B559" s="2" t="s">
         <v>105</v>
@@ -12467,12 +12564,12 @@
         <v>0</v>
       </c>
       <c r="F559" s="1" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
     </row>
     <row r="560" spans="1:6">
       <c r="A560" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B560" s="2" t="s">
         <v>107</v>
@@ -12484,12 +12581,12 @@
         <v>3</v>
       </c>
       <c r="F560" s="1" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
     </row>
     <row r="561" spans="1:6">
       <c r="A561" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B561" s="2" t="s">
         <v>109</v>
@@ -12501,12 +12598,12 @@
         <v>2</v>
       </c>
       <c r="F561" s="1" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
     </row>
     <row r="562" spans="1:6">
       <c r="A562" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B562" s="2" t="s">
         <v>111</v>
@@ -12518,12 +12615,12 @@
         <v>0</v>
       </c>
       <c r="F562" s="1" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
     </row>
     <row r="563" spans="1:6">
       <c r="A563" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B563" s="2" t="s">
         <v>113</v>
@@ -12535,12 +12632,12 @@
         <v>0</v>
       </c>
       <c r="F563" s="1" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
     </row>
     <row r="564" spans="1:6">
       <c r="A564" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B564" s="2" t="s">
         <v>115</v>
@@ -12552,12 +12649,12 @@
         <v>2</v>
       </c>
       <c r="F564" s="1" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
     </row>
     <row r="565" spans="1:6">
       <c r="A565" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B565" s="2" t="s">
         <v>117</v>
@@ -12569,12 +12666,12 @@
         <v>2</v>
       </c>
       <c r="F565" s="1" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
     </row>
     <row r="566" spans="1:6">
       <c r="A566" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B566" s="2" t="s">
         <v>119</v>
@@ -12586,12 +12683,12 @@
         <v>0</v>
       </c>
       <c r="F566" s="1" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
     </row>
     <row r="567" spans="1:6">
       <c r="A567" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B567" s="2" t="s">
         <v>121</v>
@@ -12603,12 +12700,12 @@
         <v>0</v>
       </c>
       <c r="F567" s="1" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
     </row>
     <row r="568" spans="1:6">
       <c r="A568" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B568" s="2" t="s">
         <v>123</v>
@@ -12620,12 +12717,12 @@
         <v>4</v>
       </c>
       <c r="F568" s="1" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
     </row>
     <row r="569" spans="1:6">
       <c r="A569" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B569" s="2" t="s">
         <v>125</v>
@@ -12637,12 +12734,12 @@
         <v>1</v>
       </c>
       <c r="F569" s="1" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
     </row>
     <row r="570" spans="1:6">
       <c r="A570" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B570" s="2" t="s">
         <v>127</v>
@@ -12654,97 +12751,97 @@
         <v>2</v>
       </c>
       <c r="F570" s="1" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
     </row>
     <row r="571" spans="1:6">
       <c r="A571" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B571" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C571" s="1" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="D571" s="2">
         <v>2</v>
       </c>
       <c r="F571" s="1" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
     </row>
     <row r="572" spans="1:6">
       <c r="A572" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B572" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C572" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D572" s="2">
         <v>0</v>
       </c>
       <c r="F572" s="1" t="s">
-        <v>838</v>
+        <v>831</v>
       </c>
     </row>
     <row r="573" spans="1:6">
       <c r="A573" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B573" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C573" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D573" s="2">
         <v>2</v>
       </c>
       <c r="F573" s="1" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
     </row>
     <row r="574" spans="1:6">
       <c r="A574" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B574" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C574" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D574" s="2">
         <v>1</v>
       </c>
       <c r="F574" s="1" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
     </row>
     <row r="575" spans="1:6">
       <c r="A575" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B575" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C575" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D575" s="2">
         <v>3</v>
       </c>
       <c r="F575" s="1" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
     </row>
     <row r="576" spans="1:6">
       <c r="A576" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B576" s="2" t="s">
         <v>139</v>
@@ -12756,12 +12853,12 @@
         <v>0</v>
       </c>
       <c r="F576" s="1" t="s">
-        <v>842</v>
+        <v>835</v>
       </c>
     </row>
     <row r="577" spans="1:6">
       <c r="A577" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B577" s="2" t="s">
         <v>141</v>
@@ -12773,12 +12870,12 @@
         <v>1</v>
       </c>
       <c r="F577" s="1" t="s">
-        <v>843</v>
+        <v>836</v>
       </c>
     </row>
     <row r="578" spans="1:6">
       <c r="A578" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B578" s="2" t="s">
         <v>143</v>
@@ -12790,12 +12887,12 @@
         <v>0</v>
       </c>
       <c r="F578" s="1" t="s">
-        <v>844</v>
+        <v>837</v>
       </c>
     </row>
     <row r="579" spans="1:6">
       <c r="A579" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B579" s="2" t="s">
         <v>145</v>
@@ -12807,62 +12904,63 @@
         <v>1</v>
       </c>
       <c r="F579" s="1" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
     </row>
     <row r="580" spans="1:6">
       <c r="A580" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B580" s="2" t="s">
         <v>147</v>
       </c>
       <c r="C580" s="1" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="D580" s="2">
         <v>0</v>
       </c>
       <c r="F580" s="1" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
     </row>
     <row r="581" spans="1:6">
       <c r="A581" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B581" s="2" t="s">
         <v>149</v>
       </c>
       <c r="C581" s="1" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
       <c r="D581" s="2">
         <v>1</v>
       </c>
       <c r="F581" s="1" t="s">
-        <v>847</v>
+        <v>840</v>
       </c>
     </row>
     <row r="582" spans="1:6">
       <c r="A582" s="1" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B582" s="2" t="s">
         <v>151</v>
       </c>
       <c r="C582" s="1" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="D582" s="2">
         <v>1</v>
       </c>
       <c r="F582" s="1" t="s">
-        <v>848</v>
+        <v>841</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/hololive_cards.xlsx
+++ b/hololive_cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ff824d2898a640b1/デスクトップ/hololive_cards/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="106" documentId="11_AD4D066CA252ABDACC104873B990E4B073EEDF5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63866911-93EB-4605-9166-56947E8045C4}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="11_AD4D066CA252ABDACC104873B990E4B073EEDF5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCBC7922-2C29-4BC1-87DA-18AEC8E907FE}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="480" windowWidth="12960" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-270" yWindow="930" windowWidth="17970" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2595,9 +2595,6 @@
     <t>waf-expo2024-vol2_36.jpg</t>
   </si>
   <si>
-    <t>waf-expo2024-vol2_37.jpg</t>
-  </si>
-  <si>
     <t>ホロライブ ウエハース Vol.03</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2623,6 +2620,10 @@
   </si>
   <si>
     <t>ホロライブ ウエハース EXPO2024 Vol.02</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>waf-expo2024-vol2_37.jpg</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -8752,7 +8753,7 @@
     </row>
     <row r="330" spans="1:6">
       <c r="A330" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>79</v>
@@ -8769,7 +8770,7 @@
     </row>
     <row r="331" spans="1:6">
       <c r="A331" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>81</v>
@@ -8786,7 +8787,7 @@
     </row>
     <row r="332" spans="1:6">
       <c r="A332" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>83</v>
@@ -8803,7 +8804,7 @@
     </row>
     <row r="333" spans="1:6">
       <c r="A333" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B333" s="2" t="s">
         <v>85</v>
@@ -8820,7 +8821,7 @@
     </row>
     <row r="334" spans="1:6">
       <c r="A334" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>87</v>
@@ -8837,7 +8838,7 @@
     </row>
     <row r="335" spans="1:6">
       <c r="A335" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>89</v>
@@ -8854,7 +8855,7 @@
     </row>
     <row r="336" spans="1:6">
       <c r="A336" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>91</v>
@@ -8871,7 +8872,7 @@
     </row>
     <row r="337" spans="1:6">
       <c r="A337" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>93</v>
@@ -8888,7 +8889,7 @@
     </row>
     <row r="338" spans="1:6">
       <c r="A338" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>95</v>
@@ -8905,7 +8906,7 @@
     </row>
     <row r="339" spans="1:6">
       <c r="A339" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>97</v>
@@ -8922,7 +8923,7 @@
     </row>
     <row r="340" spans="1:6">
       <c r="A340" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>99</v>
@@ -8939,7 +8940,7 @@
     </row>
     <row r="341" spans="1:6">
       <c r="A341" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>101</v>
@@ -8956,7 +8957,7 @@
     </row>
     <row r="342" spans="1:6">
       <c r="A342" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>103</v>
@@ -8973,7 +8974,7 @@
     </row>
     <row r="343" spans="1:6">
       <c r="A343" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>105</v>
@@ -8990,7 +8991,7 @@
     </row>
     <row r="344" spans="1:6">
       <c r="A344" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>107</v>
@@ -9007,7 +9008,7 @@
     </row>
     <row r="345" spans="1:6">
       <c r="A345" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>109</v>
@@ -9024,7 +9025,7 @@
     </row>
     <row r="346" spans="1:6">
       <c r="A346" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>111</v>
@@ -9041,7 +9042,7 @@
     </row>
     <row r="347" spans="1:6">
       <c r="A347" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>113</v>
@@ -9058,7 +9059,7 @@
     </row>
     <row r="348" spans="1:6">
       <c r="A348" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>115</v>
@@ -9075,7 +9076,7 @@
     </row>
     <row r="349" spans="1:6">
       <c r="A349" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B349" s="2" t="s">
         <v>117</v>
@@ -9092,7 +9093,7 @@
     </row>
     <row r="350" spans="1:6">
       <c r="A350" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>119</v>
@@ -9109,7 +9110,7 @@
     </row>
     <row r="351" spans="1:6">
       <c r="A351" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>121</v>
@@ -9126,7 +9127,7 @@
     </row>
     <row r="352" spans="1:6">
       <c r="A352" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>123</v>
@@ -9143,7 +9144,7 @@
     </row>
     <row r="353" spans="1:6">
       <c r="A353" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>125</v>
@@ -9160,7 +9161,7 @@
     </row>
     <row r="354" spans="1:6">
       <c r="A354" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>127</v>
@@ -9177,7 +9178,7 @@
     </row>
     <row r="355" spans="1:6">
       <c r="A355" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>129</v>
@@ -9194,7 +9195,7 @@
     </row>
     <row r="356" spans="1:6">
       <c r="A356" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B356" s="2" t="s">
         <v>131</v>
@@ -9211,7 +9212,7 @@
     </row>
     <row r="357" spans="1:6">
       <c r="A357" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>133</v>
@@ -9228,7 +9229,7 @@
     </row>
     <row r="358" spans="1:6">
       <c r="A358" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>135</v>
@@ -9245,7 +9246,7 @@
     </row>
     <row r="359" spans="1:6">
       <c r="A359" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>137</v>
@@ -9262,7 +9263,7 @@
     </row>
     <row r="360" spans="1:6">
       <c r="A360" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>139</v>
@@ -9279,7 +9280,7 @@
     </row>
     <row r="361" spans="1:6">
       <c r="A361" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>141</v>
@@ -9296,7 +9297,7 @@
     </row>
     <row r="362" spans="1:6">
       <c r="A362" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>143</v>
@@ -9313,7 +9314,7 @@
     </row>
     <row r="363" spans="1:6">
       <c r="A363" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>145</v>
@@ -9330,7 +9331,7 @@
     </row>
     <row r="364" spans="1:6">
       <c r="A364" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>147</v>
@@ -9347,7 +9348,7 @@
     </row>
     <row r="365" spans="1:6">
       <c r="A365" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>149</v>
@@ -9364,7 +9365,7 @@
     </row>
     <row r="366" spans="1:6">
       <c r="A366" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>151</v>
@@ -9381,7 +9382,7 @@
     </row>
     <row r="367" spans="1:6">
       <c r="A367" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>153</v>
@@ -9398,7 +9399,7 @@
     </row>
     <row r="368" spans="1:6">
       <c r="A368" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>155</v>
@@ -9415,7 +9416,7 @@
     </row>
     <row r="369" spans="1:6">
       <c r="A369" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>157</v>
@@ -9432,7 +9433,7 @@
     </row>
     <row r="370" spans="1:6">
       <c r="A370" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>159</v>
@@ -9449,7 +9450,7 @@
     </row>
     <row r="371" spans="1:6">
       <c r="A371" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>161</v>
@@ -9466,7 +9467,7 @@
     </row>
     <row r="372" spans="1:6">
       <c r="A372" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B372" s="2" t="s">
         <v>163</v>
@@ -9483,7 +9484,7 @@
     </row>
     <row r="373" spans="1:6">
       <c r="A373" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>501</v>
@@ -9500,7 +9501,7 @@
     </row>
     <row r="374" spans="1:6">
       <c r="A374" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>502</v>
@@ -9517,7 +9518,7 @@
     </row>
     <row r="375" spans="1:6">
       <c r="A375" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>503</v>
@@ -9534,7 +9535,7 @@
     </row>
     <row r="376" spans="1:6">
       <c r="A376" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B376" s="2" t="s">
         <v>504</v>
@@ -9551,7 +9552,7 @@
     </row>
     <row r="377" spans="1:6">
       <c r="A377" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B377" s="2" t="s">
         <v>505</v>
@@ -9568,7 +9569,7 @@
     </row>
     <row r="378" spans="1:6">
       <c r="A378" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>506</v>
@@ -9585,7 +9586,7 @@
     </row>
     <row r="379" spans="1:6">
       <c r="A379" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>79</v>
@@ -9602,7 +9603,7 @@
     </row>
     <row r="380" spans="1:6">
       <c r="A380" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B380" s="2" t="s">
         <v>81</v>
@@ -9619,7 +9620,7 @@
     </row>
     <row r="381" spans="1:6">
       <c r="A381" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B381" s="2" t="s">
         <v>83</v>
@@ -9636,7 +9637,7 @@
     </row>
     <row r="382" spans="1:6">
       <c r="A382" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B382" s="2" t="s">
         <v>85</v>
@@ -9653,7 +9654,7 @@
     </row>
     <row r="383" spans="1:6">
       <c r="A383" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B383" s="2" t="s">
         <v>87</v>
@@ -9670,7 +9671,7 @@
     </row>
     <row r="384" spans="1:6">
       <c r="A384" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B384" s="2" t="s">
         <v>89</v>
@@ -9687,7 +9688,7 @@
     </row>
     <row r="385" spans="1:6">
       <c r="A385" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>91</v>
@@ -9704,7 +9705,7 @@
     </row>
     <row r="386" spans="1:6">
       <c r="A386" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>93</v>
@@ -9721,7 +9722,7 @@
     </row>
     <row r="387" spans="1:6">
       <c r="A387" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B387" s="2" t="s">
         <v>95</v>
@@ -9738,7 +9739,7 @@
     </row>
     <row r="388" spans="1:6">
       <c r="A388" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B388" s="2" t="s">
         <v>97</v>
@@ -9755,7 +9756,7 @@
     </row>
     <row r="389" spans="1:6">
       <c r="A389" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B389" s="2" t="s">
         <v>99</v>
@@ -9772,7 +9773,7 @@
     </row>
     <row r="390" spans="1:6">
       <c r="A390" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B390" s="2" t="s">
         <v>101</v>
@@ -9789,7 +9790,7 @@
     </row>
     <row r="391" spans="1:6">
       <c r="A391" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B391" s="2" t="s">
         <v>103</v>
@@ -9806,7 +9807,7 @@
     </row>
     <row r="392" spans="1:6">
       <c r="A392" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B392" s="2" t="s">
         <v>105</v>
@@ -9823,7 +9824,7 @@
     </row>
     <row r="393" spans="1:6">
       <c r="A393" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B393" s="2" t="s">
         <v>107</v>
@@ -9840,7 +9841,7 @@
     </row>
     <row r="394" spans="1:6">
       <c r="A394" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B394" s="2" t="s">
         <v>109</v>
@@ -9857,7 +9858,7 @@
     </row>
     <row r="395" spans="1:6">
       <c r="A395" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B395" s="2" t="s">
         <v>111</v>
@@ -9874,7 +9875,7 @@
     </row>
     <row r="396" spans="1:6">
       <c r="A396" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B396" s="2" t="s">
         <v>113</v>
@@ -9891,7 +9892,7 @@
     </row>
     <row r="397" spans="1:6">
       <c r="A397" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B397" s="2" t="s">
         <v>115</v>
@@ -9908,7 +9909,7 @@
     </row>
     <row r="398" spans="1:6">
       <c r="A398" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B398" s="2" t="s">
         <v>117</v>
@@ -9925,7 +9926,7 @@
     </row>
     <row r="399" spans="1:6">
       <c r="A399" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B399" s="2" t="s">
         <v>119</v>
@@ -9942,7 +9943,7 @@
     </row>
     <row r="400" spans="1:6">
       <c r="A400" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B400" s="2" t="s">
         <v>121</v>
@@ -9959,7 +9960,7 @@
     </row>
     <row r="401" spans="1:6">
       <c r="A401" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>123</v>
@@ -9976,7 +9977,7 @@
     </row>
     <row r="402" spans="1:6">
       <c r="A402" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B402" s="2" t="s">
         <v>125</v>
@@ -9993,7 +9994,7 @@
     </row>
     <row r="403" spans="1:6">
       <c r="A403" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B403" s="2" t="s">
         <v>127</v>
@@ -10010,7 +10011,7 @@
     </row>
     <row r="404" spans="1:6">
       <c r="A404" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B404" s="2" t="s">
         <v>129</v>
@@ -10027,7 +10028,7 @@
     </row>
     <row r="405" spans="1:6">
       <c r="A405" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B405" s="2" t="s">
         <v>131</v>
@@ -10044,7 +10045,7 @@
     </row>
     <row r="406" spans="1:6">
       <c r="A406" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B406" s="2" t="s">
         <v>133</v>
@@ -10061,7 +10062,7 @@
     </row>
     <row r="407" spans="1:6">
       <c r="A407" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B407" s="2" t="s">
         <v>135</v>
@@ -10078,7 +10079,7 @@
     </row>
     <row r="408" spans="1:6">
       <c r="A408" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B408" s="2" t="s">
         <v>137</v>
@@ -10095,7 +10096,7 @@
     </row>
     <row r="409" spans="1:6">
       <c r="A409" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B409" s="2" t="s">
         <v>139</v>
@@ -10112,7 +10113,7 @@
     </row>
     <row r="410" spans="1:6">
       <c r="A410" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B410" s="2" t="s">
         <v>79</v>
@@ -10129,7 +10130,7 @@
     </row>
     <row r="411" spans="1:6">
       <c r="A411" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B411" s="2" t="s">
         <v>81</v>
@@ -10146,7 +10147,7 @@
     </row>
     <row r="412" spans="1:6">
       <c r="A412" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B412" s="2" t="s">
         <v>83</v>
@@ -10163,7 +10164,7 @@
     </row>
     <row r="413" spans="1:6">
       <c r="A413" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B413" s="2" t="s">
         <v>85</v>
@@ -10180,7 +10181,7 @@
     </row>
     <row r="414" spans="1:6">
       <c r="A414" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B414" s="2" t="s">
         <v>87</v>
@@ -10197,7 +10198,7 @@
     </row>
     <row r="415" spans="1:6">
       <c r="A415" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B415" s="2" t="s">
         <v>89</v>
@@ -10214,7 +10215,7 @@
     </row>
     <row r="416" spans="1:6">
       <c r="A416" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B416" s="2" t="s">
         <v>91</v>
@@ -10231,7 +10232,7 @@
     </row>
     <row r="417" spans="1:6">
       <c r="A417" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B417" s="2" t="s">
         <v>93</v>
@@ -10248,7 +10249,7 @@
     </row>
     <row r="418" spans="1:6">
       <c r="A418" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B418" s="2" t="s">
         <v>95</v>
@@ -10265,7 +10266,7 @@
     </row>
     <row r="419" spans="1:6">
       <c r="A419" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B419" s="2" t="s">
         <v>97</v>
@@ -10282,7 +10283,7 @@
     </row>
     <row r="420" spans="1:6">
       <c r="A420" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B420" s="2" t="s">
         <v>99</v>
@@ -10299,7 +10300,7 @@
     </row>
     <row r="421" spans="1:6">
       <c r="A421" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B421" s="2" t="s">
         <v>101</v>
@@ -10316,7 +10317,7 @@
     </row>
     <row r="422" spans="1:6">
       <c r="A422" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B422" s="2" t="s">
         <v>103</v>
@@ -10333,7 +10334,7 @@
     </row>
     <row r="423" spans="1:6">
       <c r="A423" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B423" s="2" t="s">
         <v>105</v>
@@ -10350,7 +10351,7 @@
     </row>
     <row r="424" spans="1:6">
       <c r="A424" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B424" s="2" t="s">
         <v>107</v>
@@ -10367,7 +10368,7 @@
     </row>
     <row r="425" spans="1:6">
       <c r="A425" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>109</v>
@@ -10384,7 +10385,7 @@
     </row>
     <row r="426" spans="1:6">
       <c r="A426" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B426" s="2" t="s">
         <v>111</v>
@@ -10401,7 +10402,7 @@
     </row>
     <row r="427" spans="1:6">
       <c r="A427" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B427" s="2" t="s">
         <v>113</v>
@@ -10418,7 +10419,7 @@
     </row>
     <row r="428" spans="1:6">
       <c r="A428" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B428" s="2" t="s">
         <v>115</v>
@@ -10435,7 +10436,7 @@
     </row>
     <row r="429" spans="1:6">
       <c r="A429" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B429" s="2" t="s">
         <v>117</v>
@@ -10452,7 +10453,7 @@
     </row>
     <row r="430" spans="1:6">
       <c r="A430" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B430" s="2" t="s">
         <v>119</v>
@@ -10469,7 +10470,7 @@
     </row>
     <row r="431" spans="1:6">
       <c r="A431" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B431" s="2" t="s">
         <v>121</v>
@@ -10486,7 +10487,7 @@
     </row>
     <row r="432" spans="1:6">
       <c r="A432" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B432" s="2" t="s">
         <v>123</v>
@@ -10503,7 +10504,7 @@
     </row>
     <row r="433" spans="1:6">
       <c r="A433" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B433" s="2" t="s">
         <v>125</v>
@@ -10520,7 +10521,7 @@
     </row>
     <row r="434" spans="1:6">
       <c r="A434" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B434" s="2" t="s">
         <v>127</v>
@@ -10537,7 +10538,7 @@
     </row>
     <row r="435" spans="1:6">
       <c r="A435" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B435" s="2" t="s">
         <v>129</v>
@@ -10554,7 +10555,7 @@
     </row>
     <row r="436" spans="1:6">
       <c r="A436" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B436" s="2" t="s">
         <v>131</v>
@@ -10571,7 +10572,7 @@
     </row>
     <row r="437" spans="1:6">
       <c r="A437" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B437" s="2" t="s">
         <v>133</v>
@@ -10588,7 +10589,7 @@
     </row>
     <row r="438" spans="1:6">
       <c r="A438" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B438" s="2" t="s">
         <v>135</v>
@@ -10605,7 +10606,7 @@
     </row>
     <row r="439" spans="1:6">
       <c r="A439" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B439" s="2" t="s">
         <v>137</v>
@@ -10622,7 +10623,7 @@
     </row>
     <row r="440" spans="1:6">
       <c r="A440" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>139</v>
@@ -10639,7 +10640,7 @@
     </row>
     <row r="441" spans="1:6">
       <c r="A441" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B441" s="2" t="s">
         <v>141</v>
@@ -10656,7 +10657,7 @@
     </row>
     <row r="442" spans="1:6">
       <c r="A442" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B442" s="2" t="s">
         <v>143</v>
@@ -10673,7 +10674,7 @@
     </row>
     <row r="443" spans="1:6">
       <c r="A443" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B443" s="2" t="s">
         <v>79</v>
@@ -10690,7 +10691,7 @@
     </row>
     <row r="444" spans="1:6">
       <c r="A444" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B444" s="2" t="s">
         <v>81</v>
@@ -10707,7 +10708,7 @@
     </row>
     <row r="445" spans="1:6">
       <c r="A445" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>83</v>
@@ -10724,7 +10725,7 @@
     </row>
     <row r="446" spans="1:6">
       <c r="A446" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B446" s="2" t="s">
         <v>85</v>
@@ -10741,7 +10742,7 @@
     </row>
     <row r="447" spans="1:6">
       <c r="A447" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B447" s="2" t="s">
         <v>87</v>
@@ -10758,7 +10759,7 @@
     </row>
     <row r="448" spans="1:6">
       <c r="A448" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B448" s="2" t="s">
         <v>89</v>
@@ -10775,7 +10776,7 @@
     </row>
     <row r="449" spans="1:6">
       <c r="A449" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B449" s="2" t="s">
         <v>91</v>
@@ -10792,7 +10793,7 @@
     </row>
     <row r="450" spans="1:6">
       <c r="A450" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B450" s="2" t="s">
         <v>93</v>
@@ -10809,7 +10810,7 @@
     </row>
     <row r="451" spans="1:6">
       <c r="A451" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B451" s="2" t="s">
         <v>95</v>
@@ -10826,7 +10827,7 @@
     </row>
     <row r="452" spans="1:6">
       <c r="A452" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B452" s="2" t="s">
         <v>97</v>
@@ -10843,7 +10844,7 @@
     </row>
     <row r="453" spans="1:6">
       <c r="A453" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B453" s="2" t="s">
         <v>99</v>
@@ -10860,7 +10861,7 @@
     </row>
     <row r="454" spans="1:6">
       <c r="A454" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B454" s="2" t="s">
         <v>101</v>
@@ -10877,7 +10878,7 @@
     </row>
     <row r="455" spans="1:6">
       <c r="A455" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B455" s="2" t="s">
         <v>103</v>
@@ -10894,7 +10895,7 @@
     </row>
     <row r="456" spans="1:6">
       <c r="A456" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B456" s="2" t="s">
         <v>105</v>
@@ -10911,7 +10912,7 @@
     </row>
     <row r="457" spans="1:6">
       <c r="A457" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B457" s="2" t="s">
         <v>107</v>
@@ -10928,7 +10929,7 @@
     </row>
     <row r="458" spans="1:6">
       <c r="A458" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B458" s="2" t="s">
         <v>109</v>
@@ -10945,7 +10946,7 @@
     </row>
     <row r="459" spans="1:6">
       <c r="A459" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B459" s="2" t="s">
         <v>111</v>
@@ -10962,7 +10963,7 @@
     </row>
     <row r="460" spans="1:6">
       <c r="A460" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B460" s="2" t="s">
         <v>113</v>
@@ -10979,7 +10980,7 @@
     </row>
     <row r="461" spans="1:6">
       <c r="A461" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B461" s="2" t="s">
         <v>115</v>
@@ -10996,7 +10997,7 @@
     </row>
     <row r="462" spans="1:6">
       <c r="A462" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B462" s="2" t="s">
         <v>117</v>
@@ -11013,7 +11014,7 @@
     </row>
     <row r="463" spans="1:6">
       <c r="A463" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B463" s="2" t="s">
         <v>119</v>
@@ -11030,7 +11031,7 @@
     </row>
     <row r="464" spans="1:6">
       <c r="A464" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B464" s="2" t="s">
         <v>121</v>
@@ -11047,7 +11048,7 @@
     </row>
     <row r="465" spans="1:6">
       <c r="A465" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B465" s="2" t="s">
         <v>123</v>
@@ -11064,7 +11065,7 @@
     </row>
     <row r="466" spans="1:6">
       <c r="A466" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B466" s="2" t="s">
         <v>125</v>
@@ -11081,7 +11082,7 @@
     </row>
     <row r="467" spans="1:6">
       <c r="A467" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B467" s="2" t="s">
         <v>127</v>
@@ -11098,7 +11099,7 @@
     </row>
     <row r="468" spans="1:6">
       <c r="A468" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B468" s="2" t="s">
         <v>129</v>
@@ -11115,7 +11116,7 @@
     </row>
     <row r="469" spans="1:6">
       <c r="A469" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B469" s="2" t="s">
         <v>131</v>
@@ -11132,7 +11133,7 @@
     </row>
     <row r="470" spans="1:6">
       <c r="A470" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B470" s="2" t="s">
         <v>133</v>
@@ -11149,7 +11150,7 @@
     </row>
     <row r="471" spans="1:6">
       <c r="A471" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B471" s="2" t="s">
         <v>135</v>
@@ -11166,7 +11167,7 @@
     </row>
     <row r="472" spans="1:6">
       <c r="A472" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B472" s="2" t="s">
         <v>137</v>
@@ -11183,7 +11184,7 @@
     </row>
     <row r="473" spans="1:6">
       <c r="A473" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B473" s="2" t="s">
         <v>79</v>
@@ -11197,7 +11198,7 @@
     </row>
     <row r="474" spans="1:6">
       <c r="A474" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B474" s="2" t="s">
         <v>81</v>
@@ -11211,7 +11212,7 @@
     </row>
     <row r="475" spans="1:6">
       <c r="A475" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B475" s="2" t="s">
         <v>83</v>
@@ -11225,7 +11226,7 @@
     </row>
     <row r="476" spans="1:6">
       <c r="A476" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B476" s="2" t="s">
         <v>85</v>
@@ -11239,7 +11240,7 @@
     </row>
     <row r="477" spans="1:6">
       <c r="A477" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B477" s="2" t="s">
         <v>87</v>
@@ -11253,7 +11254,7 @@
     </row>
     <row r="478" spans="1:6">
       <c r="A478" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B478" s="2" t="s">
         <v>89</v>
@@ -11267,7 +11268,7 @@
     </row>
     <row r="479" spans="1:6">
       <c r="A479" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B479" s="2" t="s">
         <v>91</v>
@@ -11281,7 +11282,7 @@
     </row>
     <row r="480" spans="1:6">
       <c r="A480" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B480" s="2" t="s">
         <v>93</v>
@@ -11295,7 +11296,7 @@
     </row>
     <row r="481" spans="1:6">
       <c r="A481" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B481" s="2" t="s">
         <v>95</v>
@@ -11309,7 +11310,7 @@
     </row>
     <row r="482" spans="1:6">
       <c r="A482" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B482" s="2" t="s">
         <v>97</v>
@@ -11323,7 +11324,7 @@
     </row>
     <row r="483" spans="1:6">
       <c r="A483" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B483" s="2" t="s">
         <v>99</v>
@@ -11337,7 +11338,7 @@
     </row>
     <row r="484" spans="1:6">
       <c r="A484" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B484" s="2" t="s">
         <v>101</v>
@@ -11351,7 +11352,7 @@
     </row>
     <row r="485" spans="1:6">
       <c r="A485" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B485" s="2" t="s">
         <v>103</v>
@@ -11365,7 +11366,7 @@
     </row>
     <row r="486" spans="1:6">
       <c r="A486" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B486" s="2" t="s">
         <v>105</v>
@@ -11379,7 +11380,7 @@
     </row>
     <row r="487" spans="1:6">
       <c r="A487" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B487" s="2" t="s">
         <v>107</v>
@@ -11393,7 +11394,7 @@
     </row>
     <row r="488" spans="1:6">
       <c r="A488" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B488" s="2" t="s">
         <v>109</v>
@@ -11407,7 +11408,7 @@
     </row>
     <row r="489" spans="1:6">
       <c r="A489" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B489" s="2" t="s">
         <v>111</v>
@@ -11421,7 +11422,7 @@
     </row>
     <row r="490" spans="1:6">
       <c r="A490" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B490" s="2" t="s">
         <v>113</v>
@@ -11435,7 +11436,7 @@
     </row>
     <row r="491" spans="1:6">
       <c r="A491" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B491" s="2" t="s">
         <v>115</v>
@@ -11449,7 +11450,7 @@
     </row>
     <row r="492" spans="1:6">
       <c r="A492" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B492" s="2" t="s">
         <v>117</v>
@@ -11463,7 +11464,7 @@
     </row>
     <row r="493" spans="1:6">
       <c r="A493" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B493" s="2" t="s">
         <v>119</v>
@@ -11477,7 +11478,7 @@
     </row>
     <row r="494" spans="1:6">
       <c r="A494" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B494" s="2" t="s">
         <v>121</v>
@@ -11491,7 +11492,7 @@
     </row>
     <row r="495" spans="1:6">
       <c r="A495" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B495" s="2" t="s">
         <v>123</v>
@@ -11505,7 +11506,7 @@
     </row>
     <row r="496" spans="1:6">
       <c r="A496" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B496" s="2" t="s">
         <v>125</v>
@@ -11519,7 +11520,7 @@
     </row>
     <row r="497" spans="1:6">
       <c r="A497" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>127</v>
@@ -11533,7 +11534,7 @@
     </row>
     <row r="498" spans="1:6">
       <c r="A498" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B498" s="2" t="s">
         <v>129</v>
@@ -11547,7 +11548,7 @@
     </row>
     <row r="499" spans="1:6">
       <c r="A499" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B499" s="2" t="s">
         <v>131</v>
@@ -11561,7 +11562,7 @@
     </row>
     <row r="500" spans="1:6">
       <c r="A500" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B500" s="2" t="s">
         <v>133</v>
@@ -11575,7 +11576,7 @@
     </row>
     <row r="501" spans="1:6">
       <c r="A501" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B501" s="2" t="s">
         <v>135</v>
@@ -11589,7 +11590,7 @@
     </row>
     <row r="502" spans="1:6">
       <c r="A502" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>137</v>
@@ -11603,7 +11604,7 @@
     </row>
     <row r="503" spans="1:6">
       <c r="A503" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B503" s="2" t="s">
         <v>139</v>
@@ -11617,7 +11618,7 @@
     </row>
     <row r="504" spans="1:6">
       <c r="A504" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B504" s="2" t="s">
         <v>141</v>
@@ -11631,7 +11632,7 @@
     </row>
     <row r="505" spans="1:6">
       <c r="A505" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B505" s="2" t="s">
         <v>79</v>
@@ -11648,7 +11649,7 @@
     </row>
     <row r="506" spans="1:6">
       <c r="A506" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B506" s="2" t="s">
         <v>81</v>
@@ -11665,7 +11666,7 @@
     </row>
     <row r="507" spans="1:6">
       <c r="A507" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B507" s="2" t="s">
         <v>83</v>
@@ -11682,7 +11683,7 @@
     </row>
     <row r="508" spans="1:6">
       <c r="A508" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B508" s="2" t="s">
         <v>85</v>
@@ -11699,7 +11700,7 @@
     </row>
     <row r="509" spans="1:6">
       <c r="A509" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B509" s="2" t="s">
         <v>87</v>
@@ -11716,7 +11717,7 @@
     </row>
     <row r="510" spans="1:6">
       <c r="A510" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B510" s="2" t="s">
         <v>89</v>
@@ -11733,7 +11734,7 @@
     </row>
     <row r="511" spans="1:6">
       <c r="A511" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B511" s="2" t="s">
         <v>91</v>
@@ -11750,7 +11751,7 @@
     </row>
     <row r="512" spans="1:6">
       <c r="A512" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B512" s="2" t="s">
         <v>93</v>
@@ -11770,7 +11771,7 @@
     </row>
     <row r="513" spans="1:6">
       <c r="A513" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B513" s="2" t="s">
         <v>95</v>
@@ -11787,7 +11788,7 @@
     </row>
     <row r="514" spans="1:6">
       <c r="A514" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B514" s="2" t="s">
         <v>97</v>
@@ -11804,7 +11805,7 @@
     </row>
     <row r="515" spans="1:6">
       <c r="A515" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B515" s="2" t="s">
         <v>99</v>
@@ -11821,7 +11822,7 @@
     </row>
     <row r="516" spans="1:6">
       <c r="A516" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B516" s="2" t="s">
         <v>101</v>
@@ -11838,7 +11839,7 @@
     </row>
     <row r="517" spans="1:6">
       <c r="A517" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B517" s="2" t="s">
         <v>103</v>
@@ -11855,7 +11856,7 @@
     </row>
     <row r="518" spans="1:6">
       <c r="A518" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B518" s="2" t="s">
         <v>105</v>
@@ -11872,7 +11873,7 @@
     </row>
     <row r="519" spans="1:6">
       <c r="A519" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B519" s="2" t="s">
         <v>107</v>
@@ -11889,7 +11890,7 @@
     </row>
     <row r="520" spans="1:6">
       <c r="A520" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B520" s="2" t="s">
         <v>109</v>
@@ -11906,7 +11907,7 @@
     </row>
     <row r="521" spans="1:6">
       <c r="A521" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B521" s="2" t="s">
         <v>111</v>
@@ -11923,7 +11924,7 @@
     </row>
     <row r="522" spans="1:6">
       <c r="A522" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B522" s="2" t="s">
         <v>113</v>
@@ -11940,7 +11941,7 @@
     </row>
     <row r="523" spans="1:6">
       <c r="A523" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B523" s="2" t="s">
         <v>115</v>
@@ -11957,7 +11958,7 @@
     </row>
     <row r="524" spans="1:6">
       <c r="A524" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B524" s="2" t="s">
         <v>117</v>
@@ -11974,7 +11975,7 @@
     </row>
     <row r="525" spans="1:6">
       <c r="A525" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B525" s="2" t="s">
         <v>119</v>
@@ -11991,7 +11992,7 @@
     </row>
     <row r="526" spans="1:6">
       <c r="A526" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B526" s="2" t="s">
         <v>121</v>
@@ -12008,7 +12009,7 @@
     </row>
     <row r="527" spans="1:6">
       <c r="A527" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B527" s="2" t="s">
         <v>123</v>
@@ -12025,7 +12026,7 @@
     </row>
     <row r="528" spans="1:6">
       <c r="A528" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B528" s="2" t="s">
         <v>125</v>
@@ -12042,7 +12043,7 @@
     </row>
     <row r="529" spans="1:6">
       <c r="A529" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B529" s="2" t="s">
         <v>127</v>
@@ -12059,7 +12060,7 @@
     </row>
     <row r="530" spans="1:6">
       <c r="A530" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>129</v>
@@ -12076,7 +12077,7 @@
     </row>
     <row r="531" spans="1:6">
       <c r="A531" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B531" s="2" t="s">
         <v>131</v>
@@ -12093,7 +12094,7 @@
     </row>
     <row r="532" spans="1:6">
       <c r="A532" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B532" s="2" t="s">
         <v>133</v>
@@ -12110,7 +12111,7 @@
     </row>
     <row r="533" spans="1:6">
       <c r="A533" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B533" s="2" t="s">
         <v>135</v>
@@ -12127,7 +12128,7 @@
     </row>
     <row r="534" spans="1:6">
       <c r="A534" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B534" s="2" t="s">
         <v>137</v>
@@ -12144,7 +12145,7 @@
     </row>
     <row r="535" spans="1:6">
       <c r="A535" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B535" s="2" t="s">
         <v>139</v>
@@ -12161,7 +12162,7 @@
     </row>
     <row r="536" spans="1:6">
       <c r="A536" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B536" s="2" t="s">
         <v>141</v>
@@ -12178,7 +12179,7 @@
     </row>
     <row r="537" spans="1:6">
       <c r="A537" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B537" s="2" t="s">
         <v>143</v>
@@ -12195,7 +12196,7 @@
     </row>
     <row r="538" spans="1:6">
       <c r="A538" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B538" s="2" t="s">
         <v>145</v>
@@ -12212,7 +12213,7 @@
     </row>
     <row r="539" spans="1:6">
       <c r="A539" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B539" s="2" t="s">
         <v>147</v>
@@ -12229,7 +12230,7 @@
     </row>
     <row r="540" spans="1:6">
       <c r="A540" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B540" s="2" t="s">
         <v>149</v>
@@ -12246,7 +12247,7 @@
     </row>
     <row r="541" spans="1:6">
       <c r="A541" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B541" s="2" t="s">
         <v>151</v>
@@ -12263,7 +12264,7 @@
     </row>
     <row r="542" spans="1:6">
       <c r="A542" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B542" s="2" t="s">
         <v>153</v>
@@ -12280,7 +12281,7 @@
     </row>
     <row r="543" spans="1:6">
       <c r="A543" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B543" s="2" t="s">
         <v>155</v>
@@ -12297,7 +12298,7 @@
     </row>
     <row r="544" spans="1:6">
       <c r="A544" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B544" s="2" t="s">
         <v>157</v>
@@ -12314,7 +12315,7 @@
     </row>
     <row r="545" spans="1:6">
       <c r="A545" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B545" s="2" t="s">
         <v>159</v>
@@ -12331,7 +12332,7 @@
     </row>
     <row r="546" spans="1:6">
       <c r="A546" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B546" s="2" t="s">
         <v>79</v>
@@ -12348,7 +12349,7 @@
     </row>
     <row r="547" spans="1:6">
       <c r="A547" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B547" s="2" t="s">
         <v>81</v>
@@ -12365,7 +12366,7 @@
     </row>
     <row r="548" spans="1:6">
       <c r="A548" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B548" s="2" t="s">
         <v>83</v>
@@ -12382,7 +12383,7 @@
     </row>
     <row r="549" spans="1:6">
       <c r="A549" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B549" s="2" t="s">
         <v>85</v>
@@ -12399,7 +12400,7 @@
     </row>
     <row r="550" spans="1:6">
       <c r="A550" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B550" s="2" t="s">
         <v>87</v>
@@ -12416,7 +12417,7 @@
     </row>
     <row r="551" spans="1:6">
       <c r="A551" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B551" s="2" t="s">
         <v>89</v>
@@ -12433,7 +12434,7 @@
     </row>
     <row r="552" spans="1:6">
       <c r="A552" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B552" s="2" t="s">
         <v>91</v>
@@ -12450,7 +12451,7 @@
     </row>
     <row r="553" spans="1:6">
       <c r="A553" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B553" s="2" t="s">
         <v>93</v>
@@ -12467,7 +12468,7 @@
     </row>
     <row r="554" spans="1:6">
       <c r="A554" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B554" s="2" t="s">
         <v>95</v>
@@ -12484,7 +12485,7 @@
     </row>
     <row r="555" spans="1:6">
       <c r="A555" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B555" s="2" t="s">
         <v>97</v>
@@ -12501,7 +12502,7 @@
     </row>
     <row r="556" spans="1:6">
       <c r="A556" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B556" s="2" t="s">
         <v>99</v>
@@ -12518,7 +12519,7 @@
     </row>
     <row r="557" spans="1:6">
       <c r="A557" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B557" s="2" t="s">
         <v>101</v>
@@ -12535,7 +12536,7 @@
     </row>
     <row r="558" spans="1:6">
       <c r="A558" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B558" s="2" t="s">
         <v>103</v>
@@ -12552,7 +12553,7 @@
     </row>
     <row r="559" spans="1:6">
       <c r="A559" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B559" s="2" t="s">
         <v>105</v>
@@ -12569,7 +12570,7 @@
     </row>
     <row r="560" spans="1:6">
       <c r="A560" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B560" s="2" t="s">
         <v>107</v>
@@ -12586,7 +12587,7 @@
     </row>
     <row r="561" spans="1:6">
       <c r="A561" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B561" s="2" t="s">
         <v>109</v>
@@ -12603,7 +12604,7 @@
     </row>
     <row r="562" spans="1:6">
       <c r="A562" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B562" s="2" t="s">
         <v>111</v>
@@ -12620,7 +12621,7 @@
     </row>
     <row r="563" spans="1:6">
       <c r="A563" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B563" s="2" t="s">
         <v>113</v>
@@ -12637,7 +12638,7 @@
     </row>
     <row r="564" spans="1:6">
       <c r="A564" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B564" s="2" t="s">
         <v>115</v>
@@ -12654,7 +12655,7 @@
     </row>
     <row r="565" spans="1:6">
       <c r="A565" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B565" s="2" t="s">
         <v>117</v>
@@ -12671,7 +12672,7 @@
     </row>
     <row r="566" spans="1:6">
       <c r="A566" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B566" s="2" t="s">
         <v>119</v>
@@ -12688,7 +12689,7 @@
     </row>
     <row r="567" spans="1:6">
       <c r="A567" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B567" s="2" t="s">
         <v>121</v>
@@ -12705,7 +12706,7 @@
     </row>
     <row r="568" spans="1:6">
       <c r="A568" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B568" s="2" t="s">
         <v>123</v>
@@ -12722,7 +12723,7 @@
     </row>
     <row r="569" spans="1:6">
       <c r="A569" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B569" s="2" t="s">
         <v>125</v>
@@ -12739,7 +12740,7 @@
     </row>
     <row r="570" spans="1:6">
       <c r="A570" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B570" s="2" t="s">
         <v>127</v>
@@ -12756,7 +12757,7 @@
     </row>
     <row r="571" spans="1:6">
       <c r="A571" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B571" s="2" t="s">
         <v>129</v>
@@ -12773,7 +12774,7 @@
     </row>
     <row r="572" spans="1:6">
       <c r="A572" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B572" s="2" t="s">
         <v>131</v>
@@ -12790,7 +12791,7 @@
     </row>
     <row r="573" spans="1:6">
       <c r="A573" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B573" s="2" t="s">
         <v>133</v>
@@ -12807,7 +12808,7 @@
     </row>
     <row r="574" spans="1:6">
       <c r="A574" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B574" s="2" t="s">
         <v>135</v>
@@ -12824,7 +12825,7 @@
     </row>
     <row r="575" spans="1:6">
       <c r="A575" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B575" s="2" t="s">
         <v>137</v>
@@ -12841,7 +12842,7 @@
     </row>
     <row r="576" spans="1:6">
       <c r="A576" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B576" s="2" t="s">
         <v>139</v>
@@ -12858,7 +12859,7 @@
     </row>
     <row r="577" spans="1:6">
       <c r="A577" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B577" s="2" t="s">
         <v>141</v>
@@ -12875,7 +12876,7 @@
     </row>
     <row r="578" spans="1:6">
       <c r="A578" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B578" s="2" t="s">
         <v>143</v>
@@ -12892,7 +12893,7 @@
     </row>
     <row r="579" spans="1:6">
       <c r="A579" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B579" s="2" t="s">
         <v>145</v>
@@ -12909,7 +12910,7 @@
     </row>
     <row r="580" spans="1:6">
       <c r="A580" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B580" s="2" t="s">
         <v>147</v>
@@ -12926,7 +12927,7 @@
     </row>
     <row r="581" spans="1:6">
       <c r="A581" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B581" s="2" t="s">
         <v>149</v>
@@ -12943,7 +12944,7 @@
     </row>
     <row r="582" spans="1:6">
       <c r="A582" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B582" s="2" t="s">
         <v>151</v>
@@ -12955,7 +12956,7 @@
         <v>1</v>
       </c>
       <c r="F582" s="1" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
     </row>
   </sheetData>

--- a/hololive_cards.xlsx
+++ b/hololive_cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ff824d2898a640b1/デスクトップ/hololive_cards/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="11_AD4D066CA252ABDACC104873B990E4B073EEDF5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCBC7922-2C29-4BC1-87DA-18AEC8E907FE}"/>
+  <xr:revisionPtr revIDLastSave="109" documentId="11_AD4D066CA252ABDACC104873B990E4B073EEDF5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8E86717-A5AC-49F7-93D9-F19120F93952}"/>
   <bookViews>
-    <workbookView xWindow="-270" yWindow="930" windowWidth="17970" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="75" yWindow="1245" windowWidth="17970" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2615,15 +2615,15 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ホロライブ ウエハース EXPO2024 Vol.01</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ホロライブ ウエハース EXPO2024 Vol.02</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>waf-expo2024-vol2_37.jpg</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ホロライブ ウエハース EXPO2024 vol.01</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -11632,7 +11632,7 @@
     </row>
     <row r="505" spans="1:6">
       <c r="A505" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B505" s="2" t="s">
         <v>79</v>
@@ -11649,7 +11649,7 @@
     </row>
     <row r="506" spans="1:6">
       <c r="A506" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B506" s="2" t="s">
         <v>81</v>
@@ -11666,7 +11666,7 @@
     </row>
     <row r="507" spans="1:6">
       <c r="A507" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B507" s="2" t="s">
         <v>83</v>
@@ -11683,7 +11683,7 @@
     </row>
     <row r="508" spans="1:6">
       <c r="A508" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B508" s="2" t="s">
         <v>85</v>
@@ -11700,7 +11700,7 @@
     </row>
     <row r="509" spans="1:6">
       <c r="A509" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B509" s="2" t="s">
         <v>87</v>
@@ -11717,7 +11717,7 @@
     </row>
     <row r="510" spans="1:6">
       <c r="A510" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B510" s="2" t="s">
         <v>89</v>
@@ -11734,7 +11734,7 @@
     </row>
     <row r="511" spans="1:6">
       <c r="A511" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B511" s="2" t="s">
         <v>91</v>
@@ -11751,7 +11751,7 @@
     </row>
     <row r="512" spans="1:6">
       <c r="A512" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B512" s="2" t="s">
         <v>93</v>
@@ -11771,7 +11771,7 @@
     </row>
     <row r="513" spans="1:6">
       <c r="A513" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B513" s="2" t="s">
         <v>95</v>
@@ -11788,7 +11788,7 @@
     </row>
     <row r="514" spans="1:6">
       <c r="A514" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B514" s="2" t="s">
         <v>97</v>
@@ -11805,7 +11805,7 @@
     </row>
     <row r="515" spans="1:6">
       <c r="A515" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B515" s="2" t="s">
         <v>99</v>
@@ -11822,7 +11822,7 @@
     </row>
     <row r="516" spans="1:6">
       <c r="A516" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B516" s="2" t="s">
         <v>101</v>
@@ -11839,7 +11839,7 @@
     </row>
     <row r="517" spans="1:6">
       <c r="A517" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B517" s="2" t="s">
         <v>103</v>
@@ -11856,7 +11856,7 @@
     </row>
     <row r="518" spans="1:6">
       <c r="A518" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B518" s="2" t="s">
         <v>105</v>
@@ -11873,7 +11873,7 @@
     </row>
     <row r="519" spans="1:6">
       <c r="A519" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B519" s="2" t="s">
         <v>107</v>
@@ -11890,7 +11890,7 @@
     </row>
     <row r="520" spans="1:6">
       <c r="A520" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B520" s="2" t="s">
         <v>109</v>
@@ -11907,7 +11907,7 @@
     </row>
     <row r="521" spans="1:6">
       <c r="A521" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B521" s="2" t="s">
         <v>111</v>
@@ -11924,7 +11924,7 @@
     </row>
     <row r="522" spans="1:6">
       <c r="A522" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B522" s="2" t="s">
         <v>113</v>
@@ -11941,7 +11941,7 @@
     </row>
     <row r="523" spans="1:6">
       <c r="A523" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B523" s="2" t="s">
         <v>115</v>
@@ -11958,7 +11958,7 @@
     </row>
     <row r="524" spans="1:6">
       <c r="A524" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B524" s="2" t="s">
         <v>117</v>
@@ -11975,7 +11975,7 @@
     </row>
     <row r="525" spans="1:6">
       <c r="A525" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B525" s="2" t="s">
         <v>119</v>
@@ -11992,7 +11992,7 @@
     </row>
     <row r="526" spans="1:6">
       <c r="A526" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B526" s="2" t="s">
         <v>121</v>
@@ -12009,7 +12009,7 @@
     </row>
     <row r="527" spans="1:6">
       <c r="A527" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B527" s="2" t="s">
         <v>123</v>
@@ -12026,7 +12026,7 @@
     </row>
     <row r="528" spans="1:6">
       <c r="A528" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B528" s="2" t="s">
         <v>125</v>
@@ -12043,7 +12043,7 @@
     </row>
     <row r="529" spans="1:6">
       <c r="A529" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B529" s="2" t="s">
         <v>127</v>
@@ -12060,7 +12060,7 @@
     </row>
     <row r="530" spans="1:6">
       <c r="A530" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>129</v>
@@ -12077,7 +12077,7 @@
     </row>
     <row r="531" spans="1:6">
       <c r="A531" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B531" s="2" t="s">
         <v>131</v>
@@ -12094,7 +12094,7 @@
     </row>
     <row r="532" spans="1:6">
       <c r="A532" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B532" s="2" t="s">
         <v>133</v>
@@ -12111,7 +12111,7 @@
     </row>
     <row r="533" spans="1:6">
       <c r="A533" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B533" s="2" t="s">
         <v>135</v>
@@ -12128,7 +12128,7 @@
     </row>
     <row r="534" spans="1:6">
       <c r="A534" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B534" s="2" t="s">
         <v>137</v>
@@ -12145,7 +12145,7 @@
     </row>
     <row r="535" spans="1:6">
       <c r="A535" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B535" s="2" t="s">
         <v>139</v>
@@ -12162,7 +12162,7 @@
     </row>
     <row r="536" spans="1:6">
       <c r="A536" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B536" s="2" t="s">
         <v>141</v>
@@ -12179,7 +12179,7 @@
     </row>
     <row r="537" spans="1:6">
       <c r="A537" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B537" s="2" t="s">
         <v>143</v>
@@ -12196,7 +12196,7 @@
     </row>
     <row r="538" spans="1:6">
       <c r="A538" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B538" s="2" t="s">
         <v>145</v>
@@ -12213,7 +12213,7 @@
     </row>
     <row r="539" spans="1:6">
       <c r="A539" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B539" s="2" t="s">
         <v>147</v>
@@ -12230,7 +12230,7 @@
     </row>
     <row r="540" spans="1:6">
       <c r="A540" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B540" s="2" t="s">
         <v>149</v>
@@ -12247,7 +12247,7 @@
     </row>
     <row r="541" spans="1:6">
       <c r="A541" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B541" s="2" t="s">
         <v>151</v>
@@ -12264,7 +12264,7 @@
     </row>
     <row r="542" spans="1:6">
       <c r="A542" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B542" s="2" t="s">
         <v>153</v>
@@ -12281,7 +12281,7 @@
     </row>
     <row r="543" spans="1:6">
       <c r="A543" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B543" s="2" t="s">
         <v>155</v>
@@ -12298,7 +12298,7 @@
     </row>
     <row r="544" spans="1:6">
       <c r="A544" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B544" s="2" t="s">
         <v>157</v>
@@ -12315,7 +12315,7 @@
     </row>
     <row r="545" spans="1:6">
       <c r="A545" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B545" s="2" t="s">
         <v>159</v>
@@ -12332,7 +12332,7 @@
     </row>
     <row r="546" spans="1:6">
       <c r="A546" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B546" s="2" t="s">
         <v>79</v>
@@ -12349,7 +12349,7 @@
     </row>
     <row r="547" spans="1:6">
       <c r="A547" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B547" s="2" t="s">
         <v>81</v>
@@ -12366,7 +12366,7 @@
     </row>
     <row r="548" spans="1:6">
       <c r="A548" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B548" s="2" t="s">
         <v>83</v>
@@ -12383,7 +12383,7 @@
     </row>
     <row r="549" spans="1:6">
       <c r="A549" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B549" s="2" t="s">
         <v>85</v>
@@ -12400,7 +12400,7 @@
     </row>
     <row r="550" spans="1:6">
       <c r="A550" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B550" s="2" t="s">
         <v>87</v>
@@ -12417,7 +12417,7 @@
     </row>
     <row r="551" spans="1:6">
       <c r="A551" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B551" s="2" t="s">
         <v>89</v>
@@ -12434,7 +12434,7 @@
     </row>
     <row r="552" spans="1:6">
       <c r="A552" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B552" s="2" t="s">
         <v>91</v>
@@ -12451,7 +12451,7 @@
     </row>
     <row r="553" spans="1:6">
       <c r="A553" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B553" s="2" t="s">
         <v>93</v>
@@ -12468,7 +12468,7 @@
     </row>
     <row r="554" spans="1:6">
       <c r="A554" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B554" s="2" t="s">
         <v>95</v>
@@ -12485,7 +12485,7 @@
     </row>
     <row r="555" spans="1:6">
       <c r="A555" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B555" s="2" t="s">
         <v>97</v>
@@ -12502,7 +12502,7 @@
     </row>
     <row r="556" spans="1:6">
       <c r="A556" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B556" s="2" t="s">
         <v>99</v>
@@ -12519,7 +12519,7 @@
     </row>
     <row r="557" spans="1:6">
       <c r="A557" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B557" s="2" t="s">
         <v>101</v>
@@ -12536,7 +12536,7 @@
     </row>
     <row r="558" spans="1:6">
       <c r="A558" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B558" s="2" t="s">
         <v>103</v>
@@ -12553,7 +12553,7 @@
     </row>
     <row r="559" spans="1:6">
       <c r="A559" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B559" s="2" t="s">
         <v>105</v>
@@ -12570,7 +12570,7 @@
     </row>
     <row r="560" spans="1:6">
       <c r="A560" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B560" s="2" t="s">
         <v>107</v>
@@ -12587,7 +12587,7 @@
     </row>
     <row r="561" spans="1:6">
       <c r="A561" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B561" s="2" t="s">
         <v>109</v>
@@ -12604,7 +12604,7 @@
     </row>
     <row r="562" spans="1:6">
       <c r="A562" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B562" s="2" t="s">
         <v>111</v>
@@ -12621,7 +12621,7 @@
     </row>
     <row r="563" spans="1:6">
       <c r="A563" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B563" s="2" t="s">
         <v>113</v>
@@ -12638,7 +12638,7 @@
     </row>
     <row r="564" spans="1:6">
       <c r="A564" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B564" s="2" t="s">
         <v>115</v>
@@ -12655,7 +12655,7 @@
     </row>
     <row r="565" spans="1:6">
       <c r="A565" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B565" s="2" t="s">
         <v>117</v>
@@ -12672,7 +12672,7 @@
     </row>
     <row r="566" spans="1:6">
       <c r="A566" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B566" s="2" t="s">
         <v>119</v>
@@ -12689,7 +12689,7 @@
     </row>
     <row r="567" spans="1:6">
       <c r="A567" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B567" s="2" t="s">
         <v>121</v>
@@ -12706,7 +12706,7 @@
     </row>
     <row r="568" spans="1:6">
       <c r="A568" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B568" s="2" t="s">
         <v>123</v>
@@ -12723,7 +12723,7 @@
     </row>
     <row r="569" spans="1:6">
       <c r="A569" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B569" s="2" t="s">
         <v>125</v>
@@ -12740,7 +12740,7 @@
     </row>
     <row r="570" spans="1:6">
       <c r="A570" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B570" s="2" t="s">
         <v>127</v>
@@ -12757,7 +12757,7 @@
     </row>
     <row r="571" spans="1:6">
       <c r="A571" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B571" s="2" t="s">
         <v>129</v>
@@ -12774,7 +12774,7 @@
     </row>
     <row r="572" spans="1:6">
       <c r="A572" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B572" s="2" t="s">
         <v>131</v>
@@ -12791,7 +12791,7 @@
     </row>
     <row r="573" spans="1:6">
       <c r="A573" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B573" s="2" t="s">
         <v>133</v>
@@ -12808,7 +12808,7 @@
     </row>
     <row r="574" spans="1:6">
       <c r="A574" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B574" s="2" t="s">
         <v>135</v>
@@ -12825,7 +12825,7 @@
     </row>
     <row r="575" spans="1:6">
       <c r="A575" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B575" s="2" t="s">
         <v>137</v>
@@ -12842,7 +12842,7 @@
     </row>
     <row r="576" spans="1:6">
       <c r="A576" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B576" s="2" t="s">
         <v>139</v>
@@ -12859,7 +12859,7 @@
     </row>
     <row r="577" spans="1:6">
       <c r="A577" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B577" s="2" t="s">
         <v>141</v>
@@ -12876,7 +12876,7 @@
     </row>
     <row r="578" spans="1:6">
       <c r="A578" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B578" s="2" t="s">
         <v>143</v>
@@ -12893,7 +12893,7 @@
     </row>
     <row r="579" spans="1:6">
       <c r="A579" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B579" s="2" t="s">
         <v>145</v>
@@ -12910,7 +12910,7 @@
     </row>
     <row r="580" spans="1:6">
       <c r="A580" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B580" s="2" t="s">
         <v>147</v>
@@ -12927,7 +12927,7 @@
     </row>
     <row r="581" spans="1:6">
       <c r="A581" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B581" s="2" t="s">
         <v>149</v>
@@ -12944,7 +12944,7 @@
     </row>
     <row r="582" spans="1:6">
       <c r="A582" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B582" s="2" t="s">
         <v>151</v>
@@ -12956,7 +12956,7 @@
         <v>1</v>
       </c>
       <c r="F582" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
   </sheetData>
